--- a/analysis/analysis.xlsx
+++ b/analysis/analysis.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikhi\OneDrive\Documents\GitHub\brsn_hot_hand\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3091A5D-FE5B-418F-AD54-D3ABADA3C58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFAA559-1D50-4532-9ECB-FAACE10AE751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{220D2940-96CA-40C7-A2A5-1CEE7AE4BF13}"/>
+    <workbookView xWindow="33480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{220D2940-96CA-40C7-A2A5-1CEE7AE4BF13}"/>
   </bookViews>
   <sheets>
     <sheet name="rawTable1" sheetId="12" r:id="rId1"/>
     <sheet name="parsedTable1" sheetId="1" r:id="rId2"/>
     <sheet name="finalTable1" sheetId="13" r:id="rId3"/>
-    <sheet name="rosters" sheetId="7" r:id="rId4"/>
+    <sheet name="parsedCorrections" sheetId="14" r:id="rId4"/>
+    <sheet name="finalCorrections" sheetId="15" r:id="rId5"/>
+    <sheet name="parsedDistance" sheetId="16" r:id="rId6"/>
+    <sheet name="finalDistance" sheetId="17" r:id="rId7"/>
+    <sheet name="rosters" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="320">
   <si>
     <t>athleteId</t>
   </si>
@@ -976,6 +980,51 @@
   </si>
   <si>
     <t>Weighted Means</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>distance3Misses</t>
+  </si>
+  <si>
+    <t>distance2Misses</t>
+  </si>
+  <si>
+    <t>distance1Miss</t>
+  </si>
+  <si>
+    <t>distance1Make</t>
+  </si>
+  <si>
+    <t>distance2Makes</t>
+  </si>
+  <si>
+    <t>distance3Makes</t>
+  </si>
+  <si>
+    <t>Distance|3 misses</t>
+  </si>
+  <si>
+    <t>Distance|2 misses</t>
+  </si>
+  <si>
+    <t>Distance| 1 miss</t>
+  </si>
+  <si>
+    <t>Distance</t>
+  </si>
+  <si>
+    <t>Distance|1 hit</t>
+  </si>
+  <si>
+    <t>Distance| 2 hits</t>
+  </si>
+  <si>
+    <t>Distance| 3 hits</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +1064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1023,7 +1072,6 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1383,7 +1431,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1448,7 +1496,7 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>5106247</v>
       </c>
       <c r="B2" s="1" t="str">
@@ -1463,68 +1511,68 @@
         <f>_xlfn.XLOOKUP($A2,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SR</v>
       </c>
-      <c r="E2" s="1">
-        <v>16</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.5625</v>
+      <c r="E2">
+        <v>26</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.5</v>
       </c>
       <c r="G2" s="1">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="H2" s="3">
-        <v>0.61702127659574402</v>
+        <v>0.53731343283582</v>
       </c>
       <c r="I2" s="1">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="J2" s="3">
-        <v>0.57142857142857095</v>
+        <v>0.52258064516128999</v>
       </c>
       <c r="K2" s="1">
-        <v>279</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0.51971326164874498</v>
+        <v>346</v>
+      </c>
+      <c r="L2" s="6">
+        <v>0.5</v>
       </c>
       <c r="M2" s="1">
-        <v>137</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0.452554744525547</v>
+        <v>163</v>
+      </c>
+      <c r="N2" s="6">
+        <v>0.46012269938650302</v>
       </c>
       <c r="O2" s="1">
-        <v>56</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0.46428571428571402</v>
+        <v>69</v>
+      </c>
+      <c r="P2" s="6">
+        <v>0.46376811594202899</v>
       </c>
       <c r="Q2" s="1">
-        <v>24</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0.375</v>
+        <v>30</v>
+      </c>
+      <c r="R2" s="6">
+        <v>0.4</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" ref="S2:S31" si="0">((N2*L2)-(L2*L2))/(L2*(1-L2))</f>
-        <v>-0.13983004684606123</v>
+        <v>-7.975460122699396E-2</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" ref="T2:T31" si="1">SQRT(K2)*S2</f>
-        <v>-2.3356222550470571</v>
+        <v>-1.4835213379791279</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" ref="U2:U31" si="2">2*(1-_xlfn.NORM.S.DIST(ABS(T2),TRUE))</f>
-        <v>1.9510937644194648E-2</v>
+        <v>0.13793595151500226</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>5106243</v>
+      <c r="A3">
+        <v>5175900</v>
       </c>
       <c r="B3" s="1" t="str">
         <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>Adam Hinton</v>
+        <v>Jake Fiegen</v>
       </c>
       <c r="C3" s="1" t="str">
         <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$H:$H)</f>
@@ -1534,68 +1582,68 @@
         <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SR</v>
       </c>
-      <c r="E3" s="1">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.66666666666666596</v>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.625</v>
       </c>
       <c r="G3" s="1">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H3" s="3">
-        <v>0.56410256410256399</v>
+        <v>0.46</v>
       </c>
       <c r="I3" s="1">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J3" s="3">
-        <v>0.56122448979591799</v>
+        <v>0.51351351351351304</v>
       </c>
       <c r="K3" s="1">
-        <v>218</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0.490825688073394</v>
+        <v>269</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0.54646840148698805</v>
       </c>
       <c r="M3" s="1">
-        <v>97</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0.432989690721649</v>
+        <v>134</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0.58208955223880599</v>
       </c>
       <c r="O3" s="1">
-        <v>34</v>
-      </c>
-      <c r="P3" s="3">
-        <v>0.47058823529411697</v>
+        <v>70</v>
+      </c>
+      <c r="P3" s="6">
+        <v>0.55714285714285705</v>
       </c>
       <c r="Q3" s="1">
-        <v>12</v>
-      </c>
-      <c r="R3" s="3">
-        <v>0.58333333333333304</v>
+        <v>37</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0.54054054054054002</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" si="0"/>
-        <v>-0.1135878146187423</v>
+        <v>7.8541717641303341E-2</v>
       </c>
       <c r="T3" s="3">
         <f t="shared" si="1"/>
-        <v>-1.677103984644323</v>
+        <v>1.2881799483389087</v>
       </c>
       <c r="U3" s="3">
         <f t="shared" si="2"/>
-        <v>9.3522149761463114E-2</v>
+        <v>0.19768333029083585</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>5175900</v>
+      <c r="A4">
+        <v>5106243</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>Jake Fiegen</v>
+        <v>Adam Hinton</v>
       </c>
       <c r="C4" s="1" t="str">
         <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$H:$H)</f>
@@ -1605,63 +1653,63 @@
         <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SR</v>
       </c>
-      <c r="E4" s="1">
-        <v>17</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.58823529411764697</v>
+      <c r="E4">
+        <v>18</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.72222222222222199</v>
       </c>
       <c r="G4" s="1">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H4" s="3">
-        <v>0.44444444444444398</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="I4" s="1">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="J4" s="3">
-        <v>0.53488372093023195</v>
+        <v>0.53781512605042003</v>
       </c>
       <c r="K4" s="1">
-        <v>210</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0.54285714285714204</v>
+        <v>259</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0.48262548262548199</v>
       </c>
       <c r="M4" s="1">
-        <v>105</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0.56190476190476102</v>
+        <v>112</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0.44642857142857101</v>
       </c>
       <c r="O4" s="1">
-        <v>53</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0.52830188679245205</v>
+        <v>42</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0.452380952380952</v>
       </c>
       <c r="Q4" s="1">
-        <v>27</v>
-      </c>
-      <c r="R4" s="3">
-        <v>0.51851851851851805</v>
+        <v>15</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0.53333333333333299</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="0"/>
-        <v>4.166666666666656E-2</v>
+        <v>-6.9962686567163673E-2</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="1"/>
-        <v>0.6038073644245584</v>
+        <v>-1.1259428828892932</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="2"/>
-        <v>0.54597172267656013</v>
+        <v>0.26018969643981804</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>5175898</v>
       </c>
       <c r="B5" s="1" t="str">
@@ -1676,63 +1724,63 @@
         <f>_xlfn.XLOOKUP($A5,rosters!$F:$F,rosters!$N:$N)</f>
         <v>JR</v>
       </c>
-      <c r="E5" s="1">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.36363636363636298</v>
+      </c>
+      <c r="G5" s="1">
+        <v>28</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.39285714285714202</v>
+      </c>
+      <c r="I5" s="1">
+        <v>70</v>
+      </c>
+      <c r="J5" s="3">
         <v>0.4</v>
       </c>
-      <c r="G5" s="1">
-        <v>22</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.31818181818181801</v>
-      </c>
-      <c r="I5" s="1">
-        <v>54</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0.38888888888888801</v>
-      </c>
       <c r="K5" s="1">
-        <v>131</v>
-      </c>
-      <c r="L5" s="3">
-        <v>0.465648854961832</v>
+        <v>170</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0.47058823529411697</v>
       </c>
       <c r="M5" s="1">
-        <v>54</v>
-      </c>
-      <c r="N5" s="3">
-        <v>0.53703703703703698</v>
+        <v>72</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.52777777777777701</v>
       </c>
       <c r="O5" s="1">
-        <v>26</v>
-      </c>
-      <c r="P5" s="3">
-        <v>0.42307692307692302</v>
+        <v>34</v>
+      </c>
+      <c r="P5" s="6">
+        <v>0.5</v>
       </c>
       <c r="Q5" s="1">
-        <v>10</v>
-      </c>
-      <c r="R5" s="3">
-        <v>0.3</v>
+        <v>15</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0.4</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="0"/>
-        <v>0.13359788359788352</v>
+        <v>0.10802469135802437</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="1"/>
-        <v>1.5290976684764797</v>
+        <v>1.4084696554450125</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" si="2"/>
-        <v>0.12624023327637635</v>
+        <v>0.15899204616790508</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>5106245</v>
       </c>
       <c r="B6" s="1" t="str">
@@ -1747,63 +1795,63 @@
         <f>_xlfn.XLOOKUP($A6,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SR</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>10</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="6">
         <v>0.5</v>
       </c>
       <c r="G6" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" s="3">
-        <v>0.41666666666666602</v>
+        <v>0.46153846153846101</v>
       </c>
       <c r="I6" s="1">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J6" s="3">
-        <v>0.45614035087719201</v>
+        <v>0.46031746031746001</v>
       </c>
       <c r="K6" s="1">
-        <v>119</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0.42857142857142799</v>
+        <v>138</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0.44927536231884002</v>
       </c>
       <c r="M6" s="1">
-        <v>42</v>
-      </c>
-      <c r="N6" s="3">
-        <v>0.40476190476190399</v>
+        <v>50</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0.44</v>
       </c>
       <c r="O6" s="1">
-        <v>13</v>
-      </c>
-      <c r="P6" s="3">
-        <v>0.30769230769230699</v>
+        <v>17</v>
+      </c>
+      <c r="P6" s="6">
+        <v>0.41176470588235198</v>
       </c>
       <c r="Q6" s="1">
-        <v>4</v>
-      </c>
-      <c r="R6" s="3">
-        <v>0.25</v>
+        <v>6</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0.33333333333333298</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="0"/>
-        <v>-4.1666666666666949E-2</v>
+        <v>-1.6842105263156895E-2</v>
       </c>
       <c r="T6" s="3">
         <f t="shared" si="1"/>
-        <v>-0.45452967144315781</v>
+        <v>-0.19784993893844266</v>
       </c>
       <c r="U6" s="3">
         <f t="shared" si="2"/>
-        <v>0.64944764086358675</v>
+        <v>0.84316247275660317</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>5176404</v>
       </c>
       <c r="B7" s="1" t="str">
@@ -1818,10 +1866,10 @@
         <f>_xlfn.XLOOKUP($A7,rosters!$F:$F,rosters!$N:$N)</f>
         <v>JR</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7">
         <v>3</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="6">
         <v>0</v>
       </c>
       <c r="G7" s="1">
@@ -1831,50 +1879,50 @@
         <v>0.4</v>
       </c>
       <c r="I7" s="1">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J7" s="3">
-        <v>0.51428571428571401</v>
+        <v>0.52631578947368396</v>
       </c>
       <c r="K7" s="1">
-        <v>86</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0.47674418604651098</v>
+        <v>98</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0.47959183673469302</v>
       </c>
       <c r="M7" s="1">
-        <v>29</v>
-      </c>
-      <c r="N7" s="3">
-        <v>0.48275862068965503</v>
+        <v>33</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0.45454545454545398</v>
       </c>
       <c r="O7" s="1">
-        <v>9</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0.55555555555555503</v>
+        <v>10</v>
+      </c>
+      <c r="P7" s="6">
+        <v>0.5</v>
       </c>
       <c r="Q7" s="1">
         <v>1</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="6">
         <v>0</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="0"/>
-        <v>1.149425287356423E-2</v>
+        <v>-4.8128342245988727E-2</v>
       </c>
       <c r="T7" s="3">
         <f t="shared" si="1"/>
-        <v>0.10659331604018989</v>
+        <v>-0.47644628037167869</v>
       </c>
       <c r="U7" s="3">
         <f t="shared" si="2"/>
-        <v>0.9151116214009325</v>
+        <v>0.63375646997963297</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>4684840</v>
       </c>
       <c r="B8" s="1" t="str">
@@ -1889,10 +1937,10 @@
         <f>_xlfn.XLOOKUP($A8,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SR</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8">
         <v>6</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="6">
         <v>0.5</v>
       </c>
       <c r="G8" s="1">
@@ -1908,49 +1956,49 @@
         <v>0.36363636363636298</v>
       </c>
       <c r="K8" s="1">
-        <v>75</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0.413333333333333</v>
+        <v>79</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0.417721518987341</v>
       </c>
       <c r="M8" s="1">
-        <v>21</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0.52380952380952295</v>
+        <v>22</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0.5</v>
       </c>
       <c r="O8" s="1">
         <v>8</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="6">
         <v>0.5</v>
       </c>
       <c r="Q8" s="1">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="6">
         <v>0.66666666666666596</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="0"/>
-        <v>0.18831168831168735</v>
+        <v>0.14130434782608806</v>
       </c>
       <c r="T8" s="3">
         <f t="shared" si="1"/>
-        <v>1.6308270590745841</v>
+        <v>1.2559405154902561</v>
       </c>
       <c r="U8" s="3">
         <f t="shared" si="2"/>
-        <v>0.10292681611512444</v>
+        <v>0.20913753772305088</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>5196671</v>
+      <c r="A9">
+        <v>5241718</v>
       </c>
       <c r="B9" s="1" t="str">
         <f>_xlfn.XLOOKUP($A9,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>Corbin Zentner</v>
+        <v>Anthony Nimani</v>
       </c>
       <c r="C9" s="1" t="str">
         <f>_xlfn.XLOOKUP($A9,rosters!$F:$F,rosters!$H:$H)</f>
@@ -1958,141 +2006,141 @@
       </c>
       <c r="D9" s="1" t="str">
         <f>_xlfn.XLOOKUP($A9,rosters!$F:$F,rosters!$N:$N)</f>
-        <v>SR</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
+        <v>SO</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="3">
-        <v>0.42857142857142799</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="I9" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J9" s="3">
-        <v>0.27777777777777701</v>
+        <v>0.6</v>
       </c>
       <c r="K9" s="1">
-        <v>53</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0.41509433962264097</v>
+        <v>74</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0.56756756756756699</v>
       </c>
       <c r="M9" s="1">
-        <v>16</v>
-      </c>
-      <c r="N9" s="3">
-        <v>0.4375</v>
+        <v>34</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0.5</v>
       </c>
       <c r="O9" s="1">
-        <v>4</v>
-      </c>
-      <c r="P9" s="3">
-        <v>0.5</v>
+        <v>11</v>
+      </c>
+      <c r="P9" s="6">
+        <v>0.45454545454545398</v>
       </c>
       <c r="Q9" s="1">
         <v>1</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
+      <c r="R9" s="6">
+        <v>1</v>
       </c>
       <c r="S9" s="3">
         <f t="shared" si="0"/>
-        <v>3.8306451612904149E-2</v>
+        <v>-0.15624999999999836</v>
       </c>
       <c r="T9" s="3">
         <f t="shared" si="1"/>
-        <v>0.27887517721034916</v>
+        <v>-1.3441133229753963</v>
       </c>
       <c r="U9" s="3">
         <f t="shared" si="2"/>
-        <v>0.78034061881764538</v>
+        <v>0.1789117444887971</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>5241716</v>
+      <c r="A10">
+        <v>5196671</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>_xlfn.XLOOKUP($A10,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>Gioacchino Panzini</v>
+        <v>Corbin Zentner</v>
       </c>
       <c r="C10" s="1" t="str">
         <f>_xlfn.XLOOKUP($A10,rosters!$F:$F,rosters!$H:$H)</f>
-        <v>F</v>
+        <v>G</v>
       </c>
       <c r="D10" s="1" t="str">
         <f>_xlfn.XLOOKUP($A10,rosters!$F:$F,rosters!$N:$N)</f>
-        <v>SO</v>
-      </c>
-      <c r="E10" s="1">
+        <v>SR</v>
+      </c>
+      <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="6">
         <v>0</v>
       </c>
       <c r="G10" s="1">
+        <v>7</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="I10" s="1">
+        <v>21</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.38095238095237999</v>
+      </c>
+      <c r="K10" s="1">
+        <v>64</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="M10" s="1">
+        <v>19</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0.36842105263157798</v>
+      </c>
+      <c r="O10" s="1">
+        <v>4</v>
+      </c>
+      <c r="P10" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Q10" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="3">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>11</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0.81818181818181801</v>
-      </c>
-      <c r="K10" s="1">
-        <v>52</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0.69230769230769196</v>
-      </c>
-      <c r="M10" s="1">
-        <v>28</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0.64285714285714202</v>
-      </c>
-      <c r="O10" s="1">
-        <v>14</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0.64285714285714202</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>6</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0.83333333333333304</v>
+      <c r="R10" s="6">
+        <v>0</v>
       </c>
       <c r="S10" s="3">
         <f t="shared" si="0"/>
-        <v>-0.16071428571428706</v>
+        <v>-6.3711911357342305E-2</v>
       </c>
       <c r="T10" s="3">
         <f t="shared" si="1"/>
-        <v>-1.1589271956848632</v>
+        <v>-0.50969529085873844</v>
       </c>
       <c r="U10" s="3">
         <f t="shared" si="2"/>
-        <v>0.24648586243810144</v>
+        <v>0.61026495265475478</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>5175897</v>
+      <c r="A11">
+        <v>5241716</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>_xlfn.XLOOKUP($A11,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>Ian Imegwu</v>
+        <v>Gioacchino Panzini</v>
       </c>
       <c r="C11" s="1" t="str">
         <f>_xlfn.XLOOKUP($A11,rosters!$F:$F,rosters!$H:$H)</f>
@@ -2100,65 +2148,65 @@
       </c>
       <c r="D11" s="1" t="str">
         <f>_xlfn.XLOOKUP($A11,rosters!$F:$F,rosters!$N:$N)</f>
-        <v>JR</v>
-      </c>
-      <c r="E11" s="1">
-        <v>3</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0.33333333333333298</v>
+        <v>SO</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H11" s="3">
-        <v>0.42857142857142799</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="3">
-        <v>0.57142857142857095</v>
+        <v>0.76923076923076905</v>
       </c>
       <c r="K11" s="1">
-        <v>52</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0.48076923076923</v>
+        <v>58</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0.67241379310344795</v>
       </c>
       <c r="M11" s="1">
-        <v>16</v>
-      </c>
-      <c r="N11" s="3">
-        <v>0.3125</v>
+        <v>30</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0.66666666666666596</v>
       </c>
       <c r="O11" s="1">
-        <v>3</v>
-      </c>
-      <c r="P11" s="3">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="P11" s="6">
+        <v>0.66666666666666596</v>
       </c>
       <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0.83333333333333304</v>
       </c>
       <c r="S11" s="3">
         <f t="shared" si="0"/>
-        <v>-0.32407407407407202</v>
+        <v>-1.7543859649124152E-2</v>
       </c>
       <c r="T11" s="3">
         <f t="shared" si="1"/>
-        <v>-2.3369313822451634</v>
+        <v>-0.13361005448885074</v>
       </c>
       <c r="U11" s="3">
         <f t="shared" si="2"/>
-        <v>1.9442752261479068E-2</v>
+        <v>0.89371093314961847</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>5241717</v>
       </c>
       <c r="B12" s="1" t="str">
@@ -2173,10 +2221,10 @@
         <f>_xlfn.XLOOKUP($A12,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SO</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="6">
         <v>0.33333333333333298</v>
       </c>
       <c r="G12" s="1">
@@ -2192,257 +2240,257 @@
         <v>0.42105263157894701</v>
       </c>
       <c r="K12" s="1">
-        <v>50</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0.48</v>
+        <v>55</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0.49090909090909002</v>
       </c>
       <c r="M12" s="1">
-        <v>18</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0.5</v>
+        <v>20</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0.55000000000000004</v>
       </c>
       <c r="O12" s="1">
-        <v>6</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0.5</v>
+        <v>7</v>
+      </c>
+      <c r="P12" s="6">
+        <v>0.57142857142857095</v>
       </c>
       <c r="Q12" s="1">
         <v>1</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="6">
         <v>1</v>
       </c>
       <c r="S12" s="3">
         <f t="shared" si="0"/>
-        <v>3.846153846153845E-2</v>
+        <v>0.11607142857143021</v>
       </c>
       <c r="T12" s="3">
         <f t="shared" si="1"/>
-        <v>0.27196414661021051</v>
+        <v>0.86080875296647308</v>
       </c>
       <c r="U12" s="3">
         <f t="shared" si="2"/>
-        <v>0.78564958745417446</v>
+        <v>0.38934338340426611</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>5241718</v>
+      <c r="A13">
+        <v>5175897</v>
       </c>
       <c r="B13" s="1" t="str">
         <f>_xlfn.XLOOKUP($A13,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>Anthony Nimani</v>
+        <v>Ian Imegwu</v>
       </c>
       <c r="C13" s="1" t="str">
         <f>_xlfn.XLOOKUP($A13,rosters!$F:$F,rosters!$H:$H)</f>
-        <v>G</v>
+        <v>F</v>
       </c>
       <c r="D13" s="1" t="str">
         <f>_xlfn.XLOOKUP($A13,rosters!$F:$F,rosters!$N:$N)</f>
-        <v>SO</v>
-      </c>
-      <c r="E13" s="1">
+        <v>JR</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G13" s="1">
+        <v>7</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="I13" s="1">
+        <v>21</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="K13" s="1">
+        <v>52</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0.48076923076923</v>
+      </c>
+      <c r="M13" s="1">
+        <v>16</v>
+      </c>
+      <c r="N13" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="O13" s="1">
+        <v>3</v>
+      </c>
+      <c r="P13" s="6">
         <v>0</v>
       </c>
-      <c r="F13" s="3">
+      <c r="Q13" s="1">
         <v>0</v>
       </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1">
-        <v>7</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0.85714285714285698</v>
-      </c>
-      <c r="K13" s="1">
-        <v>44</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0.65909090909090895</v>
-      </c>
-      <c r="M13" s="1">
-        <v>22</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0.54545454545454497</v>
-      </c>
-      <c r="O13" s="1">
-        <v>7</v>
-      </c>
-      <c r="P13" s="3">
-        <v>0.57142857142857095</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>1</v>
-      </c>
-      <c r="R13" s="3">
-        <v>1</v>
+      <c r="R13" s="6">
+        <v>0</v>
       </c>
       <c r="S13" s="3">
         <f t="shared" si="0"/>
-        <v>-0.33333333333333431</v>
+        <v>-0.32407407407407202</v>
       </c>
       <c r="T13" s="3">
         <f t="shared" si="1"/>
-        <v>-2.2110831935702731</v>
+        <v>-2.3369313822451634</v>
       </c>
       <c r="U13" s="3">
         <f t="shared" si="2"/>
-        <v>2.7030076547772008E-2</v>
+        <v>1.9442752261479068E-2</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>5313688</v>
+      <c r="A14">
+        <v>5313690</v>
       </c>
       <c r="B14" s="1" t="str">
         <f>_xlfn.XLOOKUP($A14,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>DaMaryon Fishburn</v>
+        <v>Jax Abalos</v>
       </c>
       <c r="C14" s="1" t="str">
         <f>_xlfn.XLOOKUP($A14,rosters!$F:$F,rosters!$H:$H)</f>
-        <v>G</v>
+        <v>F</v>
       </c>
       <c r="D14" s="1" t="str">
         <f>_xlfn.XLOOKUP($A14,rosters!$F:$F,rosters!$N:$N)</f>
-        <v>JR</v>
-      </c>
-      <c r="E14" s="1">
+        <v>FR</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="1">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I14" s="1">
+        <v>14</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="K14" s="1">
+        <v>28</v>
+      </c>
+      <c r="L14" s="6">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="M14" s="1">
+        <v>6</v>
+      </c>
+      <c r="N14" s="6">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="O14" s="1">
+        <v>2</v>
+      </c>
+      <c r="P14" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Q14" s="1">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>26</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0.69230769230769196</v>
-      </c>
-      <c r="M14" s="1">
-        <v>11</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0.72727272727272696</v>
-      </c>
-      <c r="O14" s="1">
-        <v>4</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>1</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="6">
         <v>0</v>
       </c>
       <c r="S14" s="3">
         <f t="shared" si="0"/>
-        <v>0.11363636363636349</v>
+        <v>0.41666666666666596</v>
       </c>
       <c r="T14" s="3">
         <f t="shared" si="1"/>
-        <v>0.57943403563554297</v>
+        <v>2.2047927592204886</v>
       </c>
       <c r="U14" s="3">
         <f t="shared" si="2"/>
-        <v>0.56229634409115903</v>
+        <v>2.7468640385681642E-2</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>5313690</v>
+      <c r="A15">
+        <v>5313688</v>
       </c>
       <c r="B15" s="1" t="str">
         <f>_xlfn.XLOOKUP($A15,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>Jax Abalos</v>
+        <v>DaMaryon Fishburn</v>
       </c>
       <c r="C15" s="1" t="str">
         <f>_xlfn.XLOOKUP($A15,rosters!$F:$F,rosters!$H:$H)</f>
-        <v>F</v>
+        <v>G</v>
       </c>
       <c r="D15" s="1" t="str">
         <f>_xlfn.XLOOKUP($A15,rosters!$F:$F,rosters!$N:$N)</f>
-        <v>FR</v>
-      </c>
-      <c r="E15" s="1">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.4</v>
+        <v>JR</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>27</v>
+      </c>
+      <c r="L15" s="6">
+        <v>0.70370370370370305</v>
+      </c>
+      <c r="M15" s="1">
         <v>11</v>
       </c>
-      <c r="J15" s="3">
-        <v>0.27272727272727199</v>
-      </c>
-      <c r="K15" s="1">
-        <v>24</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="M15" s="1">
-        <v>6</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0.66666666666666596</v>
+      <c r="N15" s="6">
+        <v>0.72727272727272696</v>
       </c>
       <c r="O15" s="1">
-        <v>2</v>
-      </c>
-      <c r="P15" s="3">
+        <v>4</v>
+      </c>
+      <c r="P15" s="6">
         <v>0.5</v>
       </c>
       <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
+        <v>1</v>
+      </c>
+      <c r="R15" s="6">
         <v>0</v>
       </c>
       <c r="S15" s="3">
         <f t="shared" si="0"/>
-        <v>0.38461538461538386</v>
+        <v>7.9545454545455599E-2</v>
       </c>
       <c r="T15" s="3">
         <f t="shared" si="1"/>
-        <v>1.8842228790639792</v>
+        <v>0.4133303063516694</v>
       </c>
       <c r="U15" s="3">
         <f t="shared" si="2"/>
-        <v>5.9534834058263097E-2</v>
+        <v>0.67936462855778146</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>5313691</v>
       </c>
       <c r="B16" s="1" t="str">
@@ -2457,10 +2505,10 @@
         <f>_xlfn.XLOOKUP($A16,rosters!$F:$F,rosters!$N:$N)</f>
         <v>FR</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>4</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="6">
         <v>0.25</v>
       </c>
       <c r="G16" s="1">
@@ -2478,25 +2526,25 @@
       <c r="K16" s="1">
         <v>19</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="6">
         <v>0.26315789473684198</v>
       </c>
       <c r="M16" s="1">
         <v>4</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="6">
         <v>0.5</v>
       </c>
       <c r="O16" s="1">
         <v>1</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="6">
         <v>0</v>
       </c>
       <c r="Q16" s="1">
         <v>0</v>
       </c>
-      <c r="R16" s="3">
+      <c r="R16" s="6">
         <v>0</v>
       </c>
       <c r="S16" s="3">
@@ -2513,7 +2561,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>5241719</v>
       </c>
       <c r="B17" s="1" t="str">
@@ -2528,10 +2576,10 @@
         <f>_xlfn.XLOOKUP($A17,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SO</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="6">
         <v>0</v>
       </c>
       <c r="G17" s="1">
@@ -2549,25 +2597,25 @@
       <c r="K17" s="1">
         <v>9</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="6">
         <v>0.44444444444444398</v>
       </c>
       <c r="M17" s="1">
         <v>3</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="6">
         <v>0.33333333333333298</v>
       </c>
       <c r="O17" s="1">
         <v>1</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="6">
         <v>0</v>
       </c>
       <c r="Q17" s="1">
         <v>0</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="6">
         <v>0</v>
       </c>
       <c r="S17" s="3">
@@ -2584,7 +2632,7 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>5174972</v>
       </c>
       <c r="B18" s="1" t="str">
@@ -2599,10 +2647,10 @@
         <f>_xlfn.XLOOKUP($A18,rosters!$F:$F,rosters!$N:$N)</f>
         <v>JR</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="6">
         <v>0</v>
       </c>
       <c r="G18" s="1">
@@ -2620,25 +2668,25 @@
       <c r="K18" s="1">
         <v>9</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="6">
         <v>0.33333333333333298</v>
       </c>
       <c r="M18" s="1">
         <v>1</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="6">
         <v>0</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="6">
         <v>0</v>
       </c>
       <c r="Q18" s="1">
         <v>0</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="6">
         <v>0</v>
       </c>
       <c r="S18" s="3">
@@ -3582,6 +3630,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3677,7 +3726,7 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>5106247</v>
       </c>
       <c r="B2" s="1" t="str">
@@ -3692,68 +3741,68 @@
         <f>_xlfn.XLOOKUP($A2,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SR</v>
       </c>
-      <c r="E2" s="1">
-        <v>16</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.5625</v>
+      <c r="E2">
+        <v>26</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.5</v>
       </c>
       <c r="G2" s="1">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="H2" s="3">
-        <v>0.61702127659574402</v>
+        <v>0.53731343283582</v>
       </c>
       <c r="I2" s="1">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="J2" s="3">
-        <v>0.57142857142857095</v>
+        <v>0.52258064516128999</v>
       </c>
       <c r="K2" s="1">
-        <v>279</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0.51971326164874498</v>
+        <v>346</v>
+      </c>
+      <c r="L2" s="6">
+        <v>0.5</v>
       </c>
       <c r="M2" s="1">
-        <v>137</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0.452554744525547</v>
+        <v>163</v>
+      </c>
+      <c r="N2" s="6">
+        <v>0.46012269938650302</v>
       </c>
       <c r="O2" s="1">
-        <v>56</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0.46428571428571402</v>
+        <v>69</v>
+      </c>
+      <c r="P2" s="6">
+        <v>0.46376811594202899</v>
       </c>
       <c r="Q2" s="1">
-        <v>24</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0.375</v>
+        <v>30</v>
+      </c>
+      <c r="R2" s="6">
+        <v>0.4</v>
       </c>
       <c r="S2" s="3">
         <f t="shared" ref="S2:S6" si="0">((N2*L2)-(L2*L2))/(L2*(1-L2))</f>
-        <v>-0.13983004684606123</v>
+        <v>-7.975460122699396E-2</v>
       </c>
       <c r="T2" s="3">
         <f t="shared" ref="T2:T6" si="1">SQRT(K2)*S2</f>
-        <v>-2.3356222550470571</v>
+        <v>-1.4835213379791279</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" ref="U2:U6" si="2">2*(1-_xlfn.NORM.S.DIST(ABS(T2),TRUE))</f>
-        <v>1.9510937644194648E-2</v>
+        <v>0.13793595151500226</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>5106243</v>
+      <c r="A3">
+        <v>5175900</v>
       </c>
       <c r="B3" s="1" t="str">
         <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>Adam Hinton</v>
+        <v>Jake Fiegen</v>
       </c>
       <c r="C3" s="1" t="str">
         <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$H:$H)</f>
@@ -3763,68 +3812,68 @@
         <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SR</v>
       </c>
-      <c r="E3" s="1">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.66666666666666596</v>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.625</v>
       </c>
       <c r="G3" s="1">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H3" s="3">
-        <v>0.56410256410256399</v>
+        <v>0.46</v>
       </c>
       <c r="I3" s="1">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J3" s="3">
-        <v>0.56122448979591799</v>
+        <v>0.51351351351351304</v>
       </c>
       <c r="K3" s="1">
-        <v>218</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0.490825688073394</v>
+        <v>269</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0.54646840148698805</v>
       </c>
       <c r="M3" s="1">
-        <v>97</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0.432989690721649</v>
+        <v>134</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0.58208955223880599</v>
       </c>
       <c r="O3" s="1">
-        <v>34</v>
-      </c>
-      <c r="P3" s="3">
-        <v>0.47058823529411697</v>
+        <v>70</v>
+      </c>
+      <c r="P3" s="6">
+        <v>0.55714285714285705</v>
       </c>
       <c r="Q3" s="1">
-        <v>12</v>
-      </c>
-      <c r="R3" s="3">
-        <v>0.58333333333333304</v>
+        <v>37</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0.54054054054054002</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" si="0"/>
-        <v>-0.1135878146187423</v>
+        <v>7.8541717641303341E-2</v>
       </c>
       <c r="T3" s="3">
         <f t="shared" si="1"/>
-        <v>-1.677103984644323</v>
+        <v>1.2881799483389087</v>
       </c>
       <c r="U3" s="3">
         <f t="shared" si="2"/>
-        <v>9.3522149761463114E-2</v>
+        <v>0.19768333029083585</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>5175900</v>
+      <c r="A4">
+        <v>5106243</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$M:$M)</f>
-        <v>Jake Fiegen</v>
+        <v>Adam Hinton</v>
       </c>
       <c r="C4" s="1" t="str">
         <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$H:$H)</f>
@@ -3834,63 +3883,63 @@
         <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SR</v>
       </c>
-      <c r="E4" s="1">
-        <v>17</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.58823529411764697</v>
+      <c r="E4">
+        <v>18</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.72222222222222199</v>
       </c>
       <c r="G4" s="1">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H4" s="3">
-        <v>0.44444444444444398</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="I4" s="1">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="J4" s="3">
-        <v>0.53488372093023195</v>
+        <v>0.53781512605042003</v>
       </c>
       <c r="K4" s="1">
-        <v>210</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0.54285714285714204</v>
+        <v>259</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0.48262548262548199</v>
       </c>
       <c r="M4" s="1">
-        <v>105</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0.56190476190476102</v>
+        <v>112</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0.44642857142857101</v>
       </c>
       <c r="O4" s="1">
-        <v>53</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0.52830188679245205</v>
+        <v>42</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0.452380952380952</v>
       </c>
       <c r="Q4" s="1">
-        <v>27</v>
-      </c>
-      <c r="R4" s="3">
-        <v>0.51851851851851805</v>
+        <v>15</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0.53333333333333299</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="0"/>
-        <v>4.166666666666656E-2</v>
+        <v>-6.9962686567163673E-2</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="1"/>
-        <v>0.6038073644245584</v>
+        <v>-1.1259428828892932</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="2"/>
-        <v>0.54597172267656013</v>
+        <v>0.26018969643981804</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>5175898</v>
       </c>
       <c r="B5" s="1" t="str">
@@ -3905,63 +3954,63 @@
         <f>_xlfn.XLOOKUP($A5,rosters!$F:$F,rosters!$N:$N)</f>
         <v>JR</v>
       </c>
-      <c r="E5" s="1">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.36363636363636298</v>
+      </c>
+      <c r="G5" s="1">
+        <v>28</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.39285714285714202</v>
+      </c>
+      <c r="I5" s="1">
+        <v>70</v>
+      </c>
+      <c r="J5" s="3">
         <v>0.4</v>
       </c>
-      <c r="G5" s="1">
-        <v>22</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.31818181818181801</v>
-      </c>
-      <c r="I5" s="1">
-        <v>54</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0.38888888888888801</v>
-      </c>
       <c r="K5" s="1">
-        <v>131</v>
-      </c>
-      <c r="L5" s="3">
-        <v>0.465648854961832</v>
+        <v>170</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0.47058823529411697</v>
       </c>
       <c r="M5" s="1">
-        <v>54</v>
-      </c>
-      <c r="N5" s="3">
-        <v>0.53703703703703698</v>
+        <v>72</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.52777777777777701</v>
       </c>
       <c r="O5" s="1">
-        <v>26</v>
-      </c>
-      <c r="P5" s="3">
-        <v>0.42307692307692302</v>
+        <v>34</v>
+      </c>
+      <c r="P5" s="6">
+        <v>0.5</v>
       </c>
       <c r="Q5" s="1">
-        <v>10</v>
-      </c>
-      <c r="R5" s="3">
-        <v>0.3</v>
+        <v>15</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0.4</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="0"/>
-        <v>0.13359788359788352</v>
+        <v>0.10802469135802437</v>
       </c>
       <c r="T5" s="3">
         <f t="shared" si="1"/>
-        <v>1.5290976684764797</v>
+        <v>1.4084696554450125</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" si="2"/>
-        <v>0.12624023327637635</v>
+        <v>0.15899204616790508</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>5106245</v>
       </c>
       <c r="B6" s="1" t="str">
@@ -3976,59 +4025,59 @@
         <f>_xlfn.XLOOKUP($A6,rosters!$F:$F,rosters!$N:$N)</f>
         <v>SR</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>10</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="6">
         <v>0.5</v>
       </c>
       <c r="G6" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" s="3">
-        <v>0.41666666666666602</v>
+        <v>0.46153846153846101</v>
       </c>
       <c r="I6" s="1">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J6" s="3">
-        <v>0.45614035087719201</v>
+        <v>0.46031746031746001</v>
       </c>
       <c r="K6" s="1">
-        <v>119</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0.42857142857142799</v>
+        <v>138</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0.44927536231884002</v>
       </c>
       <c r="M6" s="1">
-        <v>42</v>
-      </c>
-      <c r="N6" s="3">
-        <v>0.40476190476190399</v>
+        <v>50</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0.44</v>
       </c>
       <c r="O6" s="1">
-        <v>13</v>
-      </c>
-      <c r="P6" s="3">
-        <v>0.30769230769230699</v>
+        <v>17</v>
+      </c>
+      <c r="P6" s="6">
+        <v>0.41176470588235198</v>
       </c>
       <c r="Q6" s="1">
-        <v>4</v>
-      </c>
-      <c r="R6" s="3">
-        <v>0.25</v>
+        <v>6</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0.33333333333333298</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="0"/>
-        <v>-4.1666666666666949E-2</v>
+        <v>-1.6842105263156895E-2</v>
       </c>
       <c r="T6" s="3">
         <f t="shared" si="1"/>
-        <v>-0.45452967144315781</v>
+        <v>-0.19784993893844266</v>
       </c>
       <c r="U6" s="3">
         <f t="shared" si="2"/>
-        <v>0.64944764086358675</v>
+        <v>0.84316247275660317</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
@@ -4524,93 +4573,99 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>116</v>
+      <c r="A2" s="1" t="str">
+        <f>parsedTable1!B2</f>
+        <v>Cooper Noard</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>parsedTable1!C2</f>
+        <v>G</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f>parsedTable1!D2</f>
+        <v>SR</v>
       </c>
       <c r="D2" s="1" t="str">
         <f>ROUND(parsedTable1!F2,2)&amp;" ("&amp;parsedTable1!E2&amp;")"</f>
-        <v>0.56 (16)</v>
+        <v>0.5 (26)</v>
       </c>
       <c r="E2" s="1" t="str">
         <f>ROUND(parsedTable1!H2,2)&amp;" ("&amp;parsedTable1!G2&amp;")"</f>
-        <v>0.62 (47)</v>
+        <v>0.54 (67)</v>
       </c>
       <c r="F2" s="1" t="str">
         <f>ROUND(parsedTable1!J2,2)&amp;" ("&amp;parsedTable1!I2&amp;")"</f>
-        <v>0.57 (119)</v>
+        <v>0.52 (155)</v>
       </c>
       <c r="G2" s="1" t="str">
         <f>ROUND(parsedTable1!L2,2)&amp;" ("&amp;parsedTable1!K2&amp;")"</f>
-        <v>0.52 (279)</v>
+        <v>0.5 (346)</v>
       </c>
       <c r="H2" s="1" t="str">
         <f>ROUND(parsedTable1!N2,2)&amp;" ("&amp;parsedTable1!M2&amp;")"</f>
-        <v>0.45 (137)</v>
+        <v>0.46 (163)</v>
       </c>
       <c r="I2" s="1" t="str">
         <f>ROUND(parsedTable1!P2,2)&amp;" ("&amp;parsedTable1!O2&amp;")"</f>
-        <v>0.46 (56)</v>
+        <v>0.46 (69)</v>
       </c>
       <c r="J2" s="1" t="str">
         <f>ROUND(parsedTable1!R2,2)&amp;" ("&amp;parsedTable1!Q2&amp;")"</f>
-        <v>0.38 (24)</v>
+        <v>0.4 (30)</v>
       </c>
       <c r="K2" s="3">
         <f>parsedTable1!S2</f>
-        <v>-0.13983004684606123</v>
+        <v>-7.975460122699396E-2</v>
       </c>
       <c r="L2" s="3" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.IFS(parsedTable1!U2&lt;0.01,"**",parsedTable1!U2&lt;0.05,"**",parsedTable1!U2&gt;0.05,"")</f>
-        <v>**</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>116</v>
+      <c r="A3" s="1" t="str">
+        <f>parsedTable1!B3</f>
+        <v>Jake Fiegen</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f>parsedTable1!C3</f>
+        <v>G</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f>parsedTable1!D3</f>
+        <v>SR</v>
       </c>
       <c r="D3" s="1" t="str">
         <f>ROUND(parsedTable1!F3,2)&amp;" ("&amp;parsedTable1!E3&amp;")"</f>
-        <v>0.67 (15)</v>
+        <v>0.63 (24)</v>
       </c>
       <c r="E3" s="1" t="str">
         <f>ROUND(parsedTable1!H3,2)&amp;" ("&amp;parsedTable1!G3&amp;")"</f>
-        <v>0.56 (39)</v>
+        <v>0.46 (50)</v>
       </c>
       <c r="F3" s="1" t="str">
         <f>ROUND(parsedTable1!J3,2)&amp;" ("&amp;parsedTable1!I3&amp;")"</f>
-        <v>0.56 (98)</v>
+        <v>0.51 (111)</v>
       </c>
       <c r="G3" s="1" t="str">
         <f>ROUND(parsedTable1!L3,2)&amp;" ("&amp;parsedTable1!K3&amp;")"</f>
-        <v>0.49 (218)</v>
+        <v>0.55 (269)</v>
       </c>
       <c r="H3" s="1" t="str">
         <f>ROUND(parsedTable1!N3,2)&amp;" ("&amp;parsedTable1!M3&amp;")"</f>
-        <v>0.43 (97)</v>
+        <v>0.58 (134)</v>
       </c>
       <c r="I3" s="1" t="str">
         <f>ROUND(parsedTable1!P3,2)&amp;" ("&amp;parsedTable1!O3&amp;")"</f>
-        <v>0.47 (34)</v>
+        <v>0.56 (70)</v>
       </c>
       <c r="J3" s="1" t="str">
         <f>ROUND(parsedTable1!R3,2)&amp;" ("&amp;parsedTable1!Q3&amp;")"</f>
-        <v>0.58 (12)</v>
+        <v>0.54 (37)</v>
       </c>
       <c r="K3" s="3">
         <f>parsedTable1!S3</f>
-        <v>-0.1135878146187423</v>
+        <v>7.8541717641303341E-2</v>
       </c>
       <c r="L3" s="3" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.IFS(parsedTable1!U3&lt;0.01,"**",parsedTable1!U3&lt;0.05,"**",parsedTable1!U3&gt;0.05,"")</f>
@@ -4618,46 +4673,49 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>116</v>
+      <c r="A4" s="1" t="str">
+        <f>parsedTable1!B4</f>
+        <v>Adam Hinton</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <f>parsedTable1!C4</f>
+        <v>G</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f>parsedTable1!D4</f>
+        <v>SR</v>
       </c>
       <c r="D4" s="1" t="str">
         <f>ROUND(parsedTable1!F4,2)&amp;" ("&amp;parsedTable1!E4&amp;")"</f>
-        <v>0.59 (17)</v>
+        <v>0.72 (18)</v>
       </c>
       <c r="E4" s="1" t="str">
         <f>ROUND(parsedTable1!H4,2)&amp;" ("&amp;parsedTable1!G4&amp;")"</f>
-        <v>0.44 (36)</v>
+        <v>0.57 (49)</v>
       </c>
       <c r="F4" s="1" t="str">
         <f>ROUND(parsedTable1!J4,2)&amp;" ("&amp;parsedTable1!I4&amp;")"</f>
-        <v>0.53 (86)</v>
+        <v>0.54 (119)</v>
       </c>
       <c r="G4" s="1" t="str">
         <f>ROUND(parsedTable1!L4,2)&amp;" ("&amp;parsedTable1!K4&amp;")"</f>
-        <v>0.54 (210)</v>
+        <v>0.48 (259)</v>
       </c>
       <c r="H4" s="1" t="str">
         <f>ROUND(parsedTable1!N4,2)&amp;" ("&amp;parsedTable1!M4&amp;")"</f>
-        <v>0.56 (105)</v>
+        <v>0.45 (112)</v>
       </c>
       <c r="I4" s="1" t="str">
         <f>ROUND(parsedTable1!P4,2)&amp;" ("&amp;parsedTable1!O4&amp;")"</f>
-        <v>0.53 (53)</v>
+        <v>0.45 (42)</v>
       </c>
       <c r="J4" s="1" t="str">
         <f>ROUND(parsedTable1!R4,2)&amp;" ("&amp;parsedTable1!Q4&amp;")"</f>
-        <v>0.52 (27)</v>
+        <v>0.53 (15)</v>
       </c>
       <c r="K4" s="3">
         <f>parsedTable1!S4</f>
-        <v>4.166666666666656E-2</v>
+        <v>-6.9962686567163673E-2</v>
       </c>
       <c r="L4" s="3" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.IFS(parsedTable1!U4&lt;0.01,"**",parsedTable1!U4&lt;0.05,"**",parsedTable1!U4&gt;0.05,"")</f>
@@ -4665,46 +4723,49 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>85</v>
+      <c r="A5" s="1" t="str">
+        <f>parsedTable1!B5</f>
+        <v>Jacob Beccles</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f>parsedTable1!C5</f>
+        <v>G</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f>parsedTable1!D5</f>
+        <v>JR</v>
       </c>
       <c r="D5" s="1" t="str">
         <f>ROUND(parsedTable1!F5,2)&amp;" ("&amp;parsedTable1!E5&amp;")"</f>
-        <v>0.4 (10)</v>
+        <v>0.36 (11)</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>ROUND(parsedTable1!H5,2)&amp;" ("&amp;parsedTable1!G5&amp;")"</f>
-        <v>0.32 (22)</v>
+        <v>0.39 (28)</v>
       </c>
       <c r="F5" s="1" t="str">
         <f>ROUND(parsedTable1!J5,2)&amp;" ("&amp;parsedTable1!I5&amp;")"</f>
-        <v>0.39 (54)</v>
+        <v>0.4 (70)</v>
       </c>
       <c r="G5" s="1" t="str">
         <f>ROUND(parsedTable1!L5,2)&amp;" ("&amp;parsedTable1!K5&amp;")"</f>
-        <v>0.47 (131)</v>
+        <v>0.47 (170)</v>
       </c>
       <c r="H5" s="1" t="str">
         <f>ROUND(parsedTable1!N5,2)&amp;" ("&amp;parsedTable1!M5&amp;")"</f>
-        <v>0.54 (54)</v>
+        <v>0.53 (72)</v>
       </c>
       <c r="I5" s="1" t="str">
         <f>ROUND(parsedTable1!P5,2)&amp;" ("&amp;parsedTable1!O5&amp;")"</f>
-        <v>0.42 (26)</v>
+        <v>0.5 (34)</v>
       </c>
       <c r="J5" s="1" t="str">
         <f>ROUND(parsedTable1!R5,2)&amp;" ("&amp;parsedTable1!Q5&amp;")"</f>
-        <v>0.3 (10)</v>
+        <v>0.4 (15)</v>
       </c>
       <c r="K5" s="3">
         <f>parsedTable1!S5</f>
-        <v>0.13359788359788352</v>
+        <v>0.10802469135802437</v>
       </c>
       <c r="L5" s="3" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.IFS(parsedTable1!U5&lt;0.01,"**",parsedTable1!U5&lt;0.05,"**",parsedTable1!U5&gt;0.05,"")</f>
@@ -4712,14 +4773,17 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>116</v>
+      <c r="A6" s="1" t="str">
+        <f>parsedTable1!B6</f>
+        <v>Josh Baldwin</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f>parsedTable1!C6</f>
+        <v>G</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f>parsedTable1!D6</f>
+        <v>SR</v>
       </c>
       <c r="D6" s="1" t="str">
         <f>ROUND(parsedTable1!F6,2)&amp;" ("&amp;parsedTable1!E6&amp;")"</f>
@@ -4727,31 +4791,31 @@
       </c>
       <c r="E6" s="1" t="str">
         <f>ROUND(parsedTable1!H6,2)&amp;" ("&amp;parsedTable1!G6&amp;")"</f>
-        <v>0.42 (24)</v>
+        <v>0.46 (26)</v>
       </c>
       <c r="F6" s="1" t="str">
         <f>ROUND(parsedTable1!J6,2)&amp;" ("&amp;parsedTable1!I6&amp;")"</f>
-        <v>0.46 (57)</v>
+        <v>0.46 (63)</v>
       </c>
       <c r="G6" s="1" t="str">
         <f>ROUND(parsedTable1!L6,2)&amp;" ("&amp;parsedTable1!K6&amp;")"</f>
-        <v>0.43 (119)</v>
+        <v>0.45 (138)</v>
       </c>
       <c r="H6" s="1" t="str">
         <f>ROUND(parsedTable1!N6,2)&amp;" ("&amp;parsedTable1!M6&amp;")"</f>
-        <v>0.4 (42)</v>
+        <v>0.44 (50)</v>
       </c>
       <c r="I6" s="1" t="str">
         <f>ROUND(parsedTable1!P6,2)&amp;" ("&amp;parsedTable1!O6&amp;")"</f>
-        <v>0.31 (13)</v>
+        <v>0.41 (17)</v>
       </c>
       <c r="J6" s="1" t="str">
         <f>ROUND(parsedTable1!R6,2)&amp;" ("&amp;parsedTable1!Q6&amp;")"</f>
-        <v>0.25 (4)</v>
+        <v>0.33 (6)</v>
       </c>
       <c r="K6" s="3">
         <f>parsedTable1!S6</f>
-        <v>-4.1666666666666949E-2</v>
+        <v>-1.6842105263156895E-2</v>
       </c>
       <c r="L6" s="3" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.IFS(parsedTable1!U6&lt;0.01,"**",parsedTable1!U6&lt;0.05,"**",parsedTable1!U6&gt;0.05,"")</f>
@@ -4759,14 +4823,17 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>116</v>
+      <c r="A7" s="1" t="str">
+        <f>parsedTable1!B7</f>
+        <v>Emily Pape</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f>parsedTable1!C7</f>
+        <v>F</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>parsedTable1!D7</f>
+        <v>SR</v>
       </c>
       <c r="D7" s="1" t="str">
         <f>ROUND(parsedTable1!F7,2)&amp;" ("&amp;parsedTable1!E7&amp;")"</f>
@@ -4806,14 +4873,17 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>85</v>
+      <c r="A8" s="1" t="str">
+        <f>parsedTable1!B8</f>
+        <v>Rachel Kaus</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f>parsedTable1!C8</f>
+        <v>G</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f>parsedTable1!D8</f>
+        <v>JR</v>
       </c>
       <c r="D8" s="1" t="str">
         <f>ROUND(parsedTable1!F8,2)&amp;" ("&amp;parsedTable1!E8&amp;")"</f>
@@ -4853,14 +4923,17 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>85</v>
+      <c r="A9" s="1" t="str">
+        <f>parsedTable1!B9</f>
+        <v>Clarke Jackson</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>parsedTable1!C9</f>
+        <v>G</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f>parsedTable1!D9</f>
+        <v>JR</v>
       </c>
       <c r="D9" s="1" t="str">
         <f>ROUND(parsedTable1!F9,2)&amp;" ("&amp;parsedTable1!E9&amp;")"</f>
@@ -4900,14 +4973,17 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>42</v>
+      <c r="A10" s="1" t="str">
+        <f>parsedTable1!B10</f>
+        <v>Paige Engels</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>parsedTable1!C10</f>
+        <v>G</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f>parsedTable1!D10</f>
+        <v>SO</v>
       </c>
       <c r="D10" s="1" t="str">
         <f>ROUND(parsedTable1!F10,2)&amp;" ("&amp;parsedTable1!E10&amp;")"</f>
@@ -4947,14 +5023,17 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>42</v>
+      <c r="A11" s="1" t="str">
+        <f>parsedTable1!B11</f>
+        <v>Audrey Chen</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>parsedTable1!C11</f>
+        <v>G</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f>parsedTable1!D11</f>
+        <v>SO</v>
       </c>
       <c r="D11" s="1" t="str">
         <f>ROUND(parsedTable1!F11,2)&amp;" ("&amp;parsedTable1!E11&amp;")"</f>
@@ -5007,35 +5086,35 @@
       <c r="C13" s="1"/>
       <c r="D13" s="5">
         <f>SUMPRODUCT(parsedTable1!F2:F11,parsedTable1!E2:E11)/SUM(parsedTable1!E2:E11)</f>
-        <v>0.49999999999999967</v>
+        <v>0.50753768844221081</v>
       </c>
       <c r="E13" s="5">
         <f>SUMPRODUCT(parsedTable1!H2:H11,parsedTable1!G2:G11)/SUM(parsedTable1!G2:G11)</f>
-        <v>0.46572104018912502</v>
+        <v>0.46947368421052593</v>
       </c>
       <c r="F13" s="5">
         <f>SUMPRODUCT(parsedTable1!J2:J11,parsedTable1!I2:I11)/SUM(parsedTable1!I2:I11)</f>
-        <v>0.45999999999999969</v>
+        <v>0.4554079696394685</v>
       </c>
       <c r="G13" s="5">
         <f>SUMPRODUCT(parsedTable1!L2:L11,parsedTable1!K2:K11)/SUM(parsedTable1!K2:K11)</f>
-        <v>0.44851485148514814</v>
+        <v>0.45211581291759423</v>
       </c>
       <c r="H13" s="5">
         <f>SUMPRODUCT(parsedTable1!N2:N11,parsedTable1!M2:M11)/SUM(parsedTable1!M2:M11)</f>
-        <v>0.43425814234016824</v>
+        <v>0.44756756756756716</v>
       </c>
       <c r="I13" s="5">
         <f>SUMPRODUCT(parsedTable1!P2:P11,parsedTable1!O2:O11)/SUM(parsedTable1!O2:O11)</f>
-        <v>0.42990654205607426</v>
+        <v>0.45013477088948767</v>
       </c>
       <c r="J13" s="5">
         <f>SUMPRODUCT(parsedTable1!R2:R11,parsedTable1!Q2:Q11)/SUM(parsedTable1!Q2:Q11)</f>
-        <v>0.43442622950819659</v>
+        <v>0.45270270270270252</v>
       </c>
       <c r="K13" s="3">
         <f>SUMPRODUCT(K2:K11,parsedTable1!K2:K11)/SUM(parsedTable1!K2:K11)</f>
-        <v>-4.3109557779217753E-2</v>
+        <v>-2.3673625064787755E-2</v>
       </c>
       <c r="L13" s="3"/>
     </row>
@@ -5075,6 +5154,2637 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A326A5-A4BC-45B6-A316-98279F3AABBD}">
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>5106247</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A2,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Cooper Noard</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A2,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A2,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E2">
+        <v>26</v>
+      </c>
+      <c r="F2">
+        <v>0.489530091685275</v>
+      </c>
+      <c r="G2">
+        <v>67</v>
+      </c>
+      <c r="H2">
+        <v>0.53292302877910702</v>
+      </c>
+      <c r="I2">
+        <v>155</v>
+      </c>
+      <c r="J2">
+        <v>0.52113136979897101</v>
+      </c>
+      <c r="K2">
+        <v>346</v>
+      </c>
+      <c r="L2">
+        <v>0.5</v>
+      </c>
+      <c r="M2">
+        <v>163</v>
+      </c>
+      <c r="N2">
+        <v>0.461571974748821</v>
+      </c>
+      <c r="O2">
+        <v>69</v>
+      </c>
+      <c r="P2">
+        <v>0.46815851999874097</v>
+      </c>
+      <c r="Q2">
+        <v>30</v>
+      </c>
+      <c r="R2">
+        <v>0.41046990831472402</v>
+      </c>
+      <c r="S2" s="3">
+        <f t="shared" ref="S2:S11" si="0">((N2*L2)-(L2*L2))/(L2*(1-L2))</f>
+        <v>-7.6856050502357998E-2</v>
+      </c>
+      <c r="T2" s="3">
+        <f>SQRT(K2)*S2</f>
+        <v>-1.4296051778697736</v>
+      </c>
+      <c r="U2" s="3">
+        <f t="shared" ref="U2:U11" si="1">2*(1-_xlfn.NORM.S.DIST(ABS(T2),TRUE))</f>
+        <v>0.15283036861053301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>5175900</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Jake Fiegen</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>0.60771801327867003</v>
+      </c>
+      <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>0.45337241124092198</v>
+      </c>
+      <c r="I3">
+        <v>111</v>
+      </c>
+      <c r="J3">
+        <v>0.51147445231393396</v>
+      </c>
+      <c r="K3">
+        <v>269</v>
+      </c>
+      <c r="L3">
+        <v>0.54646840148698805</v>
+      </c>
+      <c r="M3">
+        <v>134</v>
+      </c>
+      <c r="N3">
+        <v>0.58378183432280895</v>
+      </c>
+      <c r="O3">
+        <v>70</v>
+      </c>
+      <c r="P3">
+        <v>0.56198658516133004</v>
+      </c>
+      <c r="Q3">
+        <v>37</v>
+      </c>
+      <c r="R3">
+        <v>0.55136389040891498</v>
+      </c>
+      <c r="S3" s="3">
+        <f t="shared" si="0"/>
+        <v>8.2273060924883595E-2</v>
+      </c>
+      <c r="T3" s="3">
+        <f t="shared" ref="T3:T11" si="2">SQRT(K3)*S3</f>
+        <v>1.3493785284390902</v>
+      </c>
+      <c r="U3" s="3">
+        <f t="shared" si="1"/>
+        <v>0.17721541386380957</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>5106243</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Adam Hinton</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E4">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>0.70923984953057095</v>
+      </c>
+      <c r="G4">
+        <v>49</v>
+      </c>
+      <c r="H4">
+        <v>0.56587290962216197</v>
+      </c>
+      <c r="I4">
+        <v>119</v>
+      </c>
+      <c r="J4">
+        <v>0.53594448464489397</v>
+      </c>
+      <c r="K4">
+        <v>259</v>
+      </c>
+      <c r="L4">
+        <v>0.48262548262548199</v>
+      </c>
+      <c r="M4">
+        <v>112</v>
+      </c>
+      <c r="N4">
+        <v>0.44843389901529301</v>
+      </c>
+      <c r="O4">
+        <v>42</v>
+      </c>
+      <c r="P4">
+        <v>0.45862574591796801</v>
+      </c>
+      <c r="Q4">
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <v>0.54879212542049005</v>
+      </c>
+      <c r="S4" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.608671757491745E-2</v>
+      </c>
+      <c r="T4" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.0635650652946287</v>
+      </c>
+      <c r="U4" s="3">
+        <f t="shared" si="1"/>
+        <v>0.28752577524533818</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>5175898</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A5,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Jacob Beccles</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A5,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A5,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>JR</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>0.34455663848930401</v>
+      </c>
+      <c r="G5">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>0.38466031749569402</v>
+      </c>
+      <c r="I5">
+        <v>70</v>
+      </c>
+      <c r="J5">
+        <v>0.39721545422902799</v>
+      </c>
+      <c r="K5">
+        <v>170</v>
+      </c>
+      <c r="L5">
+        <v>0.47058823529411697</v>
+      </c>
+      <c r="M5">
+        <v>72</v>
+      </c>
+      <c r="N5">
+        <v>0.53091039177011901</v>
+      </c>
+      <c r="O5">
+        <v>34</v>
+      </c>
+      <c r="P5">
+        <v>0.51000253890177905</v>
+      </c>
+      <c r="Q5">
+        <v>15</v>
+      </c>
+      <c r="R5">
+        <v>0.42579635913559699</v>
+      </c>
+      <c r="S5" s="3">
+        <f t="shared" si="0"/>
+        <v>0.11394185112133706</v>
+      </c>
+      <c r="T5" s="3">
+        <f t="shared" si="2"/>
+        <v>1.4856199797669254</v>
+      </c>
+      <c r="U5" s="3">
+        <f t="shared" si="1"/>
+        <v>0.1373796672150287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5106245</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A6,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Josh Baldwin</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A6,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A6,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>0.47852811707444398</v>
+      </c>
+      <c r="G6">
+        <v>26</v>
+      </c>
+      <c r="H6">
+        <v>0.45209690452300999</v>
+      </c>
+      <c r="I6">
+        <v>63</v>
+      </c>
+      <c r="J6">
+        <v>0.45703807811075298</v>
+      </c>
+      <c r="K6">
+        <v>138</v>
+      </c>
+      <c r="L6">
+        <v>0.44927536231884002</v>
+      </c>
+      <c r="M6">
+        <v>50</v>
+      </c>
+      <c r="N6">
+        <v>0.44401988786628499</v>
+      </c>
+      <c r="O6">
+        <v>17</v>
+      </c>
+      <c r="P6">
+        <v>0.42510255819899201</v>
+      </c>
+      <c r="Q6">
+        <v>6</v>
+      </c>
+      <c r="R6">
+        <v>0.36969892120792802</v>
+      </c>
+      <c r="S6" s="3">
+        <f t="shared" si="0"/>
+        <v>-9.5428351901656969E-3</v>
+      </c>
+      <c r="T6" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.11210293073064476</v>
+      </c>
+      <c r="U6" s="3">
+        <f t="shared" si="1"/>
+        <v>0.91074179368879182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5108938</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A7,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Emily Pape</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A7,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>F</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A7,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E7">
+        <v>36</v>
+      </c>
+      <c r="F7">
+        <v>0.41054525121286001</v>
+      </c>
+      <c r="G7">
+        <v>79</v>
+      </c>
+      <c r="H7">
+        <v>0.37661302975044297</v>
+      </c>
+      <c r="I7">
+        <v>159</v>
+      </c>
+      <c r="J7">
+        <v>0.38870912907196098</v>
+      </c>
+      <c r="K7">
+        <v>283</v>
+      </c>
+      <c r="L7">
+        <v>0.34628975265017597</v>
+      </c>
+      <c r="M7">
+        <v>97</v>
+      </c>
+      <c r="N7">
+        <v>0.29097791525893402</v>
+      </c>
+      <c r="O7">
+        <v>28</v>
+      </c>
+      <c r="P7">
+        <v>0.33060597151223298</v>
+      </c>
+      <c r="Q7">
+        <v>9</v>
+      </c>
+      <c r="R7">
+        <v>0.36395646376520102</v>
+      </c>
+      <c r="S7" s="3">
+        <f t="shared" si="0"/>
+        <v>-8.4612162063359225E-2</v>
+      </c>
+      <c r="T7" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.4233968825444416</v>
+      </c>
+      <c r="U7" s="3">
+        <f t="shared" si="1"/>
+        <v>0.15462113569749047</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5176408</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A8,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Rachel Kaus</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A8,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A8,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>JR</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>0.50639288443775698</v>
+      </c>
+      <c r="G8">
+        <v>67</v>
+      </c>
+      <c r="H8">
+        <v>0.42837013957416897</v>
+      </c>
+      <c r="I8">
+        <v>138</v>
+      </c>
+      <c r="J8">
+        <v>0.433190040679726</v>
+      </c>
+      <c r="K8">
+        <v>275</v>
+      </c>
+      <c r="L8">
+        <v>0.43636363636363601</v>
+      </c>
+      <c r="M8">
+        <v>110</v>
+      </c>
+      <c r="N8">
+        <v>0.420238885202388</v>
+      </c>
+      <c r="O8">
+        <v>41</v>
+      </c>
+      <c r="P8">
+        <v>0.34833262098221102</v>
+      </c>
+      <c r="Q8">
+        <v>10</v>
+      </c>
+      <c r="R8">
+        <v>0.51851388141952504</v>
+      </c>
+      <c r="S8" s="3">
+        <f t="shared" si="0"/>
+        <v>-2.8608429479633556E-2</v>
+      </c>
+      <c r="T8" s="3">
+        <f t="shared" si="2"/>
+        <v>-0.47441713212643449</v>
+      </c>
+      <c r="U8" s="3">
+        <f t="shared" si="1"/>
+        <v>0.63520247845114142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>5176410</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A9,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Clarke Jackson</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A9,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A9,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>JR</v>
+      </c>
+      <c r="E9">
+        <v>17</v>
+      </c>
+      <c r="F9">
+        <v>0.57473218739822596</v>
+      </c>
+      <c r="G9">
+        <v>48</v>
+      </c>
+      <c r="H9">
+        <v>0.55656401806189404</v>
+      </c>
+      <c r="I9">
+        <v>102</v>
+      </c>
+      <c r="J9">
+        <v>0.44893368832465202</v>
+      </c>
+      <c r="K9">
+        <v>227</v>
+      </c>
+      <c r="L9">
+        <v>0.46255506607929497</v>
+      </c>
+      <c r="M9">
+        <v>98</v>
+      </c>
+      <c r="N9">
+        <v>0.48196991166354503</v>
+      </c>
+      <c r="O9">
+        <v>45</v>
+      </c>
+      <c r="P9">
+        <v>0.47430982674555999</v>
+      </c>
+      <c r="Q9">
+        <v>20</v>
+      </c>
+      <c r="R9">
+        <v>0.46972555085170897</v>
+      </c>
+      <c r="S9" s="3">
+        <f t="shared" si="0"/>
+        <v>3.6124343832989826E-2</v>
+      </c>
+      <c r="T9" s="3">
+        <f t="shared" si="2"/>
+        <v>0.54426811898332228</v>
+      </c>
+      <c r="U9" s="3">
+        <f t="shared" si="1"/>
+        <v>0.58625698223963463</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>5241809</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A10,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Paige Engels</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A10,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A10,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SO</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>0.48560610967214102</v>
+      </c>
+      <c r="G10">
+        <v>31</v>
+      </c>
+      <c r="H10">
+        <v>0.54156155391093497</v>
+      </c>
+      <c r="I10">
+        <v>75</v>
+      </c>
+      <c r="J10">
+        <v>0.41081761006289202</v>
+      </c>
+      <c r="K10">
+        <v>160</v>
+      </c>
+      <c r="L10">
+        <v>0.4</v>
+      </c>
+      <c r="M10">
+        <v>58</v>
+      </c>
+      <c r="N10">
+        <v>0.33135979180221098</v>
+      </c>
+      <c r="O10">
+        <v>17</v>
+      </c>
+      <c r="P10">
+        <v>0.36651907138157602</v>
+      </c>
+      <c r="Q10">
+        <v>5</v>
+      </c>
+      <c r="R10">
+        <v>0.240767027654679</v>
+      </c>
+      <c r="S10" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.11440034699631517</v>
+      </c>
+      <c r="T10" s="3">
+        <f t="shared" si="2"/>
+        <v>-1.4470626464878329</v>
+      </c>
+      <c r="U10" s="3">
+        <f t="shared" si="1"/>
+        <v>0.14787937861417233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>5241811</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A11,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Audrey Chen</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A11,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A11,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SO</v>
+      </c>
+      <c r="E11">
+        <v>16</v>
+      </c>
+      <c r="F11">
+        <v>0.297136373898091</v>
+      </c>
+      <c r="G11">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>0.32564998019089397</v>
+      </c>
+      <c r="I11">
+        <v>62</v>
+      </c>
+      <c r="J11">
+        <v>0.351868986368712</v>
+      </c>
+      <c r="K11">
+        <v>118</v>
+      </c>
+      <c r="L11">
+        <v>0.34745762711864397</v>
+      </c>
+      <c r="M11">
+        <v>31</v>
+      </c>
+      <c r="N11">
+        <v>0.36041599491572102</v>
+      </c>
+      <c r="O11">
+        <v>8</v>
+      </c>
+      <c r="P11">
+        <v>0.39761541323969402</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1.0709217383920699</v>
+      </c>
+      <c r="S11" s="3">
+        <f t="shared" si="0"/>
+        <v>1.9858277922793335E-2</v>
+      </c>
+      <c r="T11" s="3">
+        <f t="shared" si="2"/>
+        <v>0.2157161140085514</v>
+      </c>
+      <c r="U11" s="3">
+        <f t="shared" si="1"/>
+        <v>0.82920903976767746</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446B55CF-589D-439C-B5DB-0CB92206422F}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="str">
+        <f>parsedCorrections!B2</f>
+        <v>Cooper Noard</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>parsedCorrections!C2</f>
+        <v>G</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f>parsedCorrections!D2</f>
+        <v>SR</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>ROUND(parsedCorrections!F2,2)&amp;" ("&amp;parsedCorrections!E2&amp;")"</f>
+        <v>0.49 (26)</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f>ROUND(parsedCorrections!H2,2)&amp;" ("&amp;parsedCorrections!G2&amp;")"</f>
+        <v>0.53 (67)</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f>ROUND(parsedCorrections!J2,2)&amp;" ("&amp;parsedCorrections!I2&amp;")"</f>
+        <v>0.52 (155)</v>
+      </c>
+      <c r="G2" s="1" t="str">
+        <f>ROUND(parsedCorrections!L2,2)&amp;" ("&amp;parsedCorrections!K2&amp;")"</f>
+        <v>0.5 (346)</v>
+      </c>
+      <c r="H2" s="1" t="str">
+        <f>ROUND(parsedCorrections!N2,2)&amp;" ("&amp;parsedCorrections!M2&amp;")"</f>
+        <v>0.46 (163)</v>
+      </c>
+      <c r="I2" s="1" t="str">
+        <f>ROUND(parsedCorrections!P2,2)&amp;" ("&amp;parsedCorrections!O2&amp;")"</f>
+        <v>0.47 (69)</v>
+      </c>
+      <c r="J2" s="1" t="str">
+        <f>ROUND(parsedCorrections!R2,2)&amp;" ("&amp;parsedCorrections!Q2&amp;")"</f>
+        <v>0.41 (30)</v>
+      </c>
+      <c r="K2" s="3">
+        <f>parsedCorrections!S2</f>
+        <v>-7.6856050502357998E-2</v>
+      </c>
+      <c r="L2" s="3" t="str" cm="1">
+        <f t="array" ref="L2">_xlfn.IFS(parsedCorrections!U2&lt;0.01,"**",parsedCorrections!U2&lt;0.05,"**",parsedCorrections!U2&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="str">
+        <f>parsedCorrections!B3</f>
+        <v>Jake Fiegen</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f>parsedCorrections!C3</f>
+        <v>G</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f>parsedCorrections!D3</f>
+        <v>SR</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f>ROUND(parsedCorrections!F3,2)&amp;" ("&amp;parsedCorrections!E3&amp;")"</f>
+        <v>0.61 (24)</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f>ROUND(parsedCorrections!H3,2)&amp;" ("&amp;parsedCorrections!G3&amp;")"</f>
+        <v>0.45 (50)</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <f>ROUND(parsedCorrections!J3,2)&amp;" ("&amp;parsedCorrections!I3&amp;")"</f>
+        <v>0.51 (111)</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <f>ROUND(parsedCorrections!L3,2)&amp;" ("&amp;parsedCorrections!K3&amp;")"</f>
+        <v>0.55 (269)</v>
+      </c>
+      <c r="H3" s="1" t="str">
+        <f>ROUND(parsedCorrections!N3,2)&amp;" ("&amp;parsedCorrections!M3&amp;")"</f>
+        <v>0.58 (134)</v>
+      </c>
+      <c r="I3" s="1" t="str">
+        <f>ROUND(parsedCorrections!P3,2)&amp;" ("&amp;parsedCorrections!O3&amp;")"</f>
+        <v>0.56 (70)</v>
+      </c>
+      <c r="J3" s="1" t="str">
+        <f>ROUND(parsedCorrections!R3,2)&amp;" ("&amp;parsedCorrections!Q3&amp;")"</f>
+        <v>0.55 (37)</v>
+      </c>
+      <c r="K3" s="3">
+        <f>parsedCorrections!S3</f>
+        <v>8.2273060924883595E-2</v>
+      </c>
+      <c r="L3" s="3" t="str" cm="1">
+        <f t="array" ref="L3">_xlfn.IFS(parsedCorrections!U3&lt;0.01,"**",parsedCorrections!U3&lt;0.05,"**",parsedCorrections!U3&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="str">
+        <f>parsedCorrections!B4</f>
+        <v>Adam Hinton</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <f>parsedCorrections!C4</f>
+        <v>G</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f>parsedCorrections!D4</f>
+        <v>SR</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>ROUND(parsedCorrections!F4,2)&amp;" ("&amp;parsedCorrections!E4&amp;")"</f>
+        <v>0.71 (18)</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f>ROUND(parsedCorrections!H4,2)&amp;" ("&amp;parsedCorrections!G4&amp;")"</f>
+        <v>0.57 (49)</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f>ROUND(parsedCorrections!J4,2)&amp;" ("&amp;parsedCorrections!I4&amp;")"</f>
+        <v>0.54 (119)</v>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f>ROUND(parsedCorrections!L4,2)&amp;" ("&amp;parsedCorrections!K4&amp;")"</f>
+        <v>0.48 (259)</v>
+      </c>
+      <c r="H4" s="1" t="str">
+        <f>ROUND(parsedCorrections!N4,2)&amp;" ("&amp;parsedCorrections!M4&amp;")"</f>
+        <v>0.45 (112)</v>
+      </c>
+      <c r="I4" s="1" t="str">
+        <f>ROUND(parsedCorrections!P4,2)&amp;" ("&amp;parsedCorrections!O4&amp;")"</f>
+        <v>0.46 (42)</v>
+      </c>
+      <c r="J4" s="1" t="str">
+        <f>ROUND(parsedCorrections!R4,2)&amp;" ("&amp;parsedCorrections!Q4&amp;")"</f>
+        <v>0.55 (15)</v>
+      </c>
+      <c r="K4" s="3">
+        <f>parsedCorrections!S4</f>
+        <v>-6.608671757491745E-2</v>
+      </c>
+      <c r="L4" s="3" t="str" cm="1">
+        <f t="array" ref="L4">_xlfn.IFS(parsedCorrections!U4&lt;0.01,"**",parsedCorrections!U4&lt;0.05,"**",parsedCorrections!U4&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="str">
+        <f>parsedCorrections!B5</f>
+        <v>Jacob Beccles</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f>parsedCorrections!C5</f>
+        <v>G</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f>parsedCorrections!D5</f>
+        <v>JR</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>ROUND(parsedCorrections!F5,2)&amp;" ("&amp;parsedCorrections!E5&amp;")"</f>
+        <v>0.34 (11)</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>ROUND(parsedCorrections!H5,2)&amp;" ("&amp;parsedCorrections!G5&amp;")"</f>
+        <v>0.38 (28)</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <f>ROUND(parsedCorrections!J5,2)&amp;" ("&amp;parsedCorrections!I5&amp;")"</f>
+        <v>0.4 (70)</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f>ROUND(parsedCorrections!L5,2)&amp;" ("&amp;parsedCorrections!K5&amp;")"</f>
+        <v>0.47 (170)</v>
+      </c>
+      <c r="H5" s="1" t="str">
+        <f>ROUND(parsedCorrections!N5,2)&amp;" ("&amp;parsedCorrections!M5&amp;")"</f>
+        <v>0.53 (72)</v>
+      </c>
+      <c r="I5" s="1" t="str">
+        <f>ROUND(parsedCorrections!P5,2)&amp;" ("&amp;parsedCorrections!O5&amp;")"</f>
+        <v>0.51 (34)</v>
+      </c>
+      <c r="J5" s="1" t="str">
+        <f>ROUND(parsedCorrections!R5,2)&amp;" ("&amp;parsedCorrections!Q5&amp;")"</f>
+        <v>0.43 (15)</v>
+      </c>
+      <c r="K5" s="3">
+        <f>parsedCorrections!S5</f>
+        <v>0.11394185112133706</v>
+      </c>
+      <c r="L5" s="3" t="str" cm="1">
+        <f t="array" ref="L5">_xlfn.IFS(parsedCorrections!U5&lt;0.01,"**",parsedCorrections!U5&lt;0.05,"**",parsedCorrections!U5&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="str">
+        <f>parsedCorrections!B6</f>
+        <v>Josh Baldwin</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f>parsedCorrections!C6</f>
+        <v>G</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f>parsedCorrections!D6</f>
+        <v>SR</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>ROUND(parsedCorrections!F6,2)&amp;" ("&amp;parsedCorrections!E6&amp;")"</f>
+        <v>0.48 (10)</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>ROUND(parsedCorrections!H6,2)&amp;" ("&amp;parsedCorrections!G6&amp;")"</f>
+        <v>0.45 (26)</v>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f>ROUND(parsedCorrections!J6,2)&amp;" ("&amp;parsedCorrections!I6&amp;")"</f>
+        <v>0.46 (63)</v>
+      </c>
+      <c r="G6" s="1" t="str">
+        <f>ROUND(parsedCorrections!L6,2)&amp;" ("&amp;parsedCorrections!K6&amp;")"</f>
+        <v>0.45 (138)</v>
+      </c>
+      <c r="H6" s="1" t="str">
+        <f>ROUND(parsedCorrections!N6,2)&amp;" ("&amp;parsedCorrections!M6&amp;")"</f>
+        <v>0.44 (50)</v>
+      </c>
+      <c r="I6" s="1" t="str">
+        <f>ROUND(parsedCorrections!P6,2)&amp;" ("&amp;parsedCorrections!O6&amp;")"</f>
+        <v>0.43 (17)</v>
+      </c>
+      <c r="J6" s="1" t="str">
+        <f>ROUND(parsedCorrections!R6,2)&amp;" ("&amp;parsedCorrections!Q6&amp;")"</f>
+        <v>0.37 (6)</v>
+      </c>
+      <c r="K6" s="3">
+        <f>parsedCorrections!S6</f>
+        <v>-9.5428351901656969E-3</v>
+      </c>
+      <c r="L6" s="3" t="str" cm="1">
+        <f t="array" ref="L6">_xlfn.IFS(parsedCorrections!U6&lt;0.01,"**",parsedCorrections!U6&lt;0.05,"**",parsedCorrections!U6&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="str">
+        <f>parsedCorrections!B7</f>
+        <v>Emily Pape</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f>parsedCorrections!C7</f>
+        <v>F</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>parsedCorrections!D7</f>
+        <v>SR</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>ROUND(parsedCorrections!F7,2)&amp;" ("&amp;parsedCorrections!E7&amp;")"</f>
+        <v>0.41 (36)</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>ROUND(parsedCorrections!H7,2)&amp;" ("&amp;parsedCorrections!G7&amp;")"</f>
+        <v>0.38 (79)</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f>ROUND(parsedCorrections!J7,2)&amp;" ("&amp;parsedCorrections!I7&amp;")"</f>
+        <v>0.39 (159)</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f>ROUND(parsedCorrections!L7,2)&amp;" ("&amp;parsedCorrections!K7&amp;")"</f>
+        <v>0.35 (283)</v>
+      </c>
+      <c r="H7" s="1" t="str">
+        <f>ROUND(parsedCorrections!N7,2)&amp;" ("&amp;parsedCorrections!M7&amp;")"</f>
+        <v>0.29 (97)</v>
+      </c>
+      <c r="I7" s="1" t="str">
+        <f>ROUND(parsedCorrections!P7,2)&amp;" ("&amp;parsedCorrections!O7&amp;")"</f>
+        <v>0.33 (28)</v>
+      </c>
+      <c r="J7" s="1" t="str">
+        <f>ROUND(parsedCorrections!R7,2)&amp;" ("&amp;parsedCorrections!Q7&amp;")"</f>
+        <v>0.36 (9)</v>
+      </c>
+      <c r="K7" s="3">
+        <f>parsedCorrections!S7</f>
+        <v>-8.4612162063359225E-2</v>
+      </c>
+      <c r="L7" s="3" t="str" cm="1">
+        <f t="array" ref="L7">_xlfn.IFS(parsedCorrections!U7&lt;0.01,"**",parsedCorrections!U7&lt;0.05,"**",parsedCorrections!U7&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="str">
+        <f>parsedCorrections!B8</f>
+        <v>Rachel Kaus</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f>parsedCorrections!C8</f>
+        <v>G</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f>parsedCorrections!D8</f>
+        <v>JR</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f>ROUND(parsedCorrections!F8,2)&amp;" ("&amp;parsedCorrections!E8&amp;")"</f>
+        <v>0.51 (31)</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>ROUND(parsedCorrections!H8,2)&amp;" ("&amp;parsedCorrections!G8&amp;")"</f>
+        <v>0.43 (67)</v>
+      </c>
+      <c r="F8" s="1" t="str">
+        <f>ROUND(parsedCorrections!J8,2)&amp;" ("&amp;parsedCorrections!I8&amp;")"</f>
+        <v>0.43 (138)</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f>ROUND(parsedCorrections!L8,2)&amp;" ("&amp;parsedCorrections!K8&amp;")"</f>
+        <v>0.44 (275)</v>
+      </c>
+      <c r="H8" s="1" t="str">
+        <f>ROUND(parsedCorrections!N8,2)&amp;" ("&amp;parsedCorrections!M8&amp;")"</f>
+        <v>0.42 (110)</v>
+      </c>
+      <c r="I8" s="1" t="str">
+        <f>ROUND(parsedCorrections!P8,2)&amp;" ("&amp;parsedCorrections!O8&amp;")"</f>
+        <v>0.35 (41)</v>
+      </c>
+      <c r="J8" s="1" t="str">
+        <f>ROUND(parsedCorrections!R8,2)&amp;" ("&amp;parsedCorrections!Q8&amp;")"</f>
+        <v>0.52 (10)</v>
+      </c>
+      <c r="K8" s="3">
+        <f>parsedCorrections!S8</f>
+        <v>-2.8608429479633556E-2</v>
+      </c>
+      <c r="L8" s="3" t="str" cm="1">
+        <f t="array" ref="L8">_xlfn.IFS(parsedCorrections!U8&lt;0.01,"**",parsedCorrections!U8&lt;0.05,"**",parsedCorrections!U8&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="str">
+        <f>parsedCorrections!B9</f>
+        <v>Clarke Jackson</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>parsedCorrections!C9</f>
+        <v>G</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f>parsedCorrections!D9</f>
+        <v>JR</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f>ROUND(parsedCorrections!F9,2)&amp;" ("&amp;parsedCorrections!E9&amp;")"</f>
+        <v>0.57 (17)</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f>ROUND(parsedCorrections!H9,2)&amp;" ("&amp;parsedCorrections!G9&amp;")"</f>
+        <v>0.56 (48)</v>
+      </c>
+      <c r="F9" s="1" t="str">
+        <f>ROUND(parsedCorrections!J9,2)&amp;" ("&amp;parsedCorrections!I9&amp;")"</f>
+        <v>0.45 (102)</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f>ROUND(parsedCorrections!L9,2)&amp;" ("&amp;parsedCorrections!K9&amp;")"</f>
+        <v>0.46 (227)</v>
+      </c>
+      <c r="H9" s="1" t="str">
+        <f>ROUND(parsedCorrections!N9,2)&amp;" ("&amp;parsedCorrections!M9&amp;")"</f>
+        <v>0.48 (98)</v>
+      </c>
+      <c r="I9" s="1" t="str">
+        <f>ROUND(parsedCorrections!P9,2)&amp;" ("&amp;parsedCorrections!O9&amp;")"</f>
+        <v>0.47 (45)</v>
+      </c>
+      <c r="J9" s="1" t="str">
+        <f>ROUND(parsedCorrections!R9,2)&amp;" ("&amp;parsedCorrections!Q9&amp;")"</f>
+        <v>0.47 (20)</v>
+      </c>
+      <c r="K9" s="3">
+        <f>parsedCorrections!S9</f>
+        <v>3.6124343832989826E-2</v>
+      </c>
+      <c r="L9" s="3" t="str" cm="1">
+        <f t="array" ref="L9">_xlfn.IFS(parsedCorrections!U9&lt;0.01,"**",parsedCorrections!U9&lt;0.05,"**",parsedCorrections!U9&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="str">
+        <f>parsedCorrections!B10</f>
+        <v>Paige Engels</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>parsedCorrections!C10</f>
+        <v>G</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f>parsedCorrections!D10</f>
+        <v>SO</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>ROUND(parsedCorrections!F10,2)&amp;" ("&amp;parsedCorrections!E10&amp;")"</f>
+        <v>0.49 (10)</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f>ROUND(parsedCorrections!H10,2)&amp;" ("&amp;parsedCorrections!G10&amp;")"</f>
+        <v>0.54 (31)</v>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f>ROUND(parsedCorrections!J10,2)&amp;" ("&amp;parsedCorrections!I10&amp;")"</f>
+        <v>0.41 (75)</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f>ROUND(parsedCorrections!L10,2)&amp;" ("&amp;parsedCorrections!K10&amp;")"</f>
+        <v>0.4 (160)</v>
+      </c>
+      <c r="H10" s="1" t="str">
+        <f>ROUND(parsedCorrections!N10,2)&amp;" ("&amp;parsedCorrections!M10&amp;")"</f>
+        <v>0.33 (58)</v>
+      </c>
+      <c r="I10" s="1" t="str">
+        <f>ROUND(parsedCorrections!P10,2)&amp;" ("&amp;parsedCorrections!O10&amp;")"</f>
+        <v>0.37 (17)</v>
+      </c>
+      <c r="J10" s="1" t="str">
+        <f>ROUND(parsedCorrections!R10,2)&amp;" ("&amp;parsedCorrections!Q10&amp;")"</f>
+        <v>0.24 (5)</v>
+      </c>
+      <c r="K10" s="3">
+        <f>parsedCorrections!S10</f>
+        <v>-0.11440034699631517</v>
+      </c>
+      <c r="L10" s="3" t="str" cm="1">
+        <f t="array" ref="L10">_xlfn.IFS(parsedCorrections!U10&lt;0.01,"**",parsedCorrections!U10&lt;0.05,"**",parsedCorrections!U10&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="str">
+        <f>parsedCorrections!B11</f>
+        <v>Audrey Chen</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>parsedCorrections!C11</f>
+        <v>G</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f>parsedCorrections!D11</f>
+        <v>SO</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>ROUND(parsedCorrections!F11,2)&amp;" ("&amp;parsedCorrections!E11&amp;")"</f>
+        <v>0.3 (16)</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f>ROUND(parsedCorrections!H11,2)&amp;" ("&amp;parsedCorrections!G11&amp;")"</f>
+        <v>0.33 (30)</v>
+      </c>
+      <c r="F11" s="1" t="str">
+        <f>ROUND(parsedCorrections!J11,2)&amp;" ("&amp;parsedCorrections!I11&amp;")"</f>
+        <v>0.35 (62)</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f>ROUND(parsedCorrections!L11,2)&amp;" ("&amp;parsedCorrections!K11&amp;")"</f>
+        <v>0.35 (118)</v>
+      </c>
+      <c r="H11" s="1" t="str">
+        <f>ROUND(parsedCorrections!N11,2)&amp;" ("&amp;parsedCorrections!M11&amp;")"</f>
+        <v>0.36 (31)</v>
+      </c>
+      <c r="I11" s="1" t="str">
+        <f>ROUND(parsedCorrections!P11,2)&amp;" ("&amp;parsedCorrections!O11&amp;")"</f>
+        <v>0.4 (8)</v>
+      </c>
+      <c r="J11" s="1" t="str">
+        <f>ROUND(parsedCorrections!R11,2)&amp;" ("&amp;parsedCorrections!Q11&amp;")"</f>
+        <v>1.07 (1)</v>
+      </c>
+      <c r="K11" s="3">
+        <f>parsedCorrections!S11</f>
+        <v>1.9858277922793335E-2</v>
+      </c>
+      <c r="L11" s="3" t="str" cm="1">
+        <f t="array" ref="L11">_xlfn.IFS(parsedCorrections!U11&lt;0.01,"**",parsedCorrections!U11&lt;0.05,"**",parsedCorrections!U11&gt;0.05,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>304</v>
+      </c>
+      <c r="D13" s="5">
+        <f>SUMPRODUCT(parsedCorrections!F2:F11,parsedCorrections!E2:E11)/SUM(parsedCorrections!E2:E11)</f>
+        <v>0.49504138147877602</v>
+      </c>
+      <c r="E13" s="5">
+        <f>SUMPRODUCT(parsedCorrections!H2:H11,parsedCorrections!G2:G11)/SUM(parsedCorrections!G2:G11)</f>
+        <v>0.4639020076103178</v>
+      </c>
+      <c r="F13" s="5">
+        <f>SUMPRODUCT(parsedCorrections!J2:J11,parsedCorrections!I2:I11)/SUM(parsedCorrections!I2:I11)</f>
+        <v>0.45344242141401758</v>
+      </c>
+      <c r="G13" s="5">
+        <f>SUMPRODUCT(parsedCorrections!L2:L11,parsedCorrections!K2:K11)/SUM(parsedCorrections!K2:K11)</f>
+        <v>0.45211581291759423</v>
+      </c>
+      <c r="H13" s="5">
+        <f>SUMPRODUCT(parsedCorrections!N2:N11,parsedCorrections!M2:M11)/SUM(parsedCorrections!M2:M11)</f>
+        <v>0.44993522944444558</v>
+      </c>
+      <c r="I13" s="5">
+        <f>SUMPRODUCT(parsedCorrections!P2:P11,parsedCorrections!O2:O11)/SUM(parsedCorrections!O2:O11)</f>
+        <v>0.45758869101717509</v>
+      </c>
+      <c r="J13" s="5">
+        <f>SUMPRODUCT(parsedCorrections!R2:R11,parsedCorrections!Q2:Q11)/SUM(parsedCorrections!Q2:Q11)</f>
+        <v>0.47082160048609561</v>
+      </c>
+      <c r="K13" s="3">
+        <f>SUMPRODUCT(K2:K11,parsedCorrections!K2:K11)/SUM(parsedCorrections!K2:K11)</f>
+        <v>-1.9196930578086135E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E68FCCC3-4A9E-49BA-BE29-E5148D3D2098}">
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>309</v>
+      </c>
+      <c r="K1" t="s">
+        <v>305</v>
+      </c>
+      <c r="L1" t="s">
+        <v>306</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>310</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
+        <v>312</v>
+      </c>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>5106247</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A2,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Cooper Noard</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A2,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A2,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E2">
+        <v>26</v>
+      </c>
+      <c r="F2">
+        <v>16.8682374841712</v>
+      </c>
+      <c r="G2">
+        <v>67</v>
+      </c>
+      <c r="H2">
+        <v>15.769767135830399</v>
+      </c>
+      <c r="I2">
+        <v>155</v>
+      </c>
+      <c r="J2">
+        <v>17.421236297841499</v>
+      </c>
+      <c r="K2">
+        <v>346</v>
+      </c>
+      <c r="L2">
+        <v>17.781518732549301</v>
+      </c>
+      <c r="M2">
+        <v>163</v>
+      </c>
+      <c r="N2">
+        <v>18.2568719474985</v>
+      </c>
+      <c r="O2">
+        <v>69</v>
+      </c>
+      <c r="P2">
+        <v>16.8414042057647</v>
+      </c>
+      <c r="Q2">
+        <v>30</v>
+      </c>
+      <c r="R2">
+        <v>17.316232001031899</v>
+      </c>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>5175900</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Jake Fiegen</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A3,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>11.957167361374101</v>
+      </c>
+      <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>13.355297224000999</v>
+      </c>
+      <c r="I3">
+        <v>111</v>
+      </c>
+      <c r="J3">
+        <v>14.3200975784926</v>
+      </c>
+      <c r="K3">
+        <v>269</v>
+      </c>
+      <c r="L3">
+        <v>14.890666392136801</v>
+      </c>
+      <c r="M3">
+        <v>134</v>
+      </c>
+      <c r="N3">
+        <v>14.257135453277799</v>
+      </c>
+      <c r="O3">
+        <v>70</v>
+      </c>
+      <c r="P3">
+        <v>15.121081348003599</v>
+      </c>
+      <c r="Q3">
+        <v>37</v>
+      </c>
+      <c r="R3">
+        <v>16.496007760683199</v>
+      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>5106243</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Adam Hinton</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A4,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E4">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>10.4510249528545</v>
+      </c>
+      <c r="G4">
+        <v>49</v>
+      </c>
+      <c r="H4">
+        <v>14.398264367016401</v>
+      </c>
+      <c r="I4">
+        <v>119</v>
+      </c>
+      <c r="J4">
+        <v>14.678368587689301</v>
+      </c>
+      <c r="K4">
+        <v>259</v>
+      </c>
+      <c r="L4">
+        <v>16.2727496093406</v>
+      </c>
+      <c r="M4">
+        <v>112</v>
+      </c>
+      <c r="N4">
+        <v>17.781499376929101</v>
+      </c>
+      <c r="O4">
+        <v>42</v>
+      </c>
+      <c r="P4">
+        <v>17.6663881086921</v>
+      </c>
+      <c r="Q4">
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <v>17.525981359747298</v>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>5175898</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A5,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Jacob Beccles</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A5,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A5,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>JR</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>8.1964939758635804</v>
+      </c>
+      <c r="G5">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>10.8496349333697</v>
+      </c>
+      <c r="I5">
+        <v>70</v>
+      </c>
+      <c r="J5">
+        <v>11.750334252377399</v>
+      </c>
+      <c r="K5">
+        <v>170</v>
+      </c>
+      <c r="L5">
+        <v>11.3824769792331</v>
+      </c>
+      <c r="M5">
+        <v>72</v>
+      </c>
+      <c r="N5">
+        <v>11.621871350843801</v>
+      </c>
+      <c r="O5">
+        <v>34</v>
+      </c>
+      <c r="P5">
+        <v>12.144037670995001</v>
+      </c>
+      <c r="Q5">
+        <v>15</v>
+      </c>
+      <c r="R5">
+        <v>10.866505168548199</v>
+      </c>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5106245</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A6,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Josh Baldwin</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A6,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A6,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>13.8775586321098</v>
+      </c>
+      <c r="G6">
+        <v>26</v>
+      </c>
+      <c r="H6">
+        <v>13.4028752483263</v>
+      </c>
+      <c r="I6">
+        <v>63</v>
+      </c>
+      <c r="J6">
+        <v>11.456300000614901</v>
+      </c>
+      <c r="K6">
+        <v>138</v>
+      </c>
+      <c r="L6">
+        <v>13.1195959961667</v>
+      </c>
+      <c r="M6">
+        <v>50</v>
+      </c>
+      <c r="N6">
+        <v>14.5963902656129</v>
+      </c>
+      <c r="O6">
+        <v>17</v>
+      </c>
+      <c r="P6">
+        <v>17.380117786602501</v>
+      </c>
+      <c r="Q6">
+        <v>6</v>
+      </c>
+      <c r="R6">
+        <v>14.6686340883866</v>
+      </c>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5108938</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A7,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Emily Pape</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A7,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>F</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A7,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SR</v>
+      </c>
+      <c r="E7">
+        <v>36</v>
+      </c>
+      <c r="F7">
+        <v>17.880458357416298</v>
+      </c>
+      <c r="G7">
+        <v>79</v>
+      </c>
+      <c r="H7">
+        <v>19.019056565313502</v>
+      </c>
+      <c r="I7">
+        <v>159</v>
+      </c>
+      <c r="J7">
+        <v>18.761649102858101</v>
+      </c>
+      <c r="K7">
+        <v>283</v>
+      </c>
+      <c r="L7">
+        <v>18.854445554025801</v>
+      </c>
+      <c r="M7">
+        <v>97</v>
+      </c>
+      <c r="N7">
+        <v>19.203611123897598</v>
+      </c>
+      <c r="O7">
+        <v>28</v>
+      </c>
+      <c r="P7">
+        <v>18.084264872486099</v>
+      </c>
+      <c r="Q7">
+        <v>9</v>
+      </c>
+      <c r="R7">
+        <v>16.7438282328017</v>
+      </c>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5176408</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A8,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Rachel Kaus</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A8,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A8,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>JR</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>9.8187712770280395</v>
+      </c>
+      <c r="G8">
+        <v>67</v>
+      </c>
+      <c r="H8">
+        <v>9.3222751191179594</v>
+      </c>
+      <c r="I8">
+        <v>138</v>
+      </c>
+      <c r="J8">
+        <v>8.4784820079695304</v>
+      </c>
+      <c r="K8">
+        <v>275</v>
+      </c>
+      <c r="L8">
+        <v>9.22955429869622</v>
+      </c>
+      <c r="M8">
+        <v>110</v>
+      </c>
+      <c r="N8">
+        <v>10.4482324991206</v>
+      </c>
+      <c r="O8">
+        <v>41</v>
+      </c>
+      <c r="P8">
+        <v>10.5527787183714</v>
+      </c>
+      <c r="Q8">
+        <v>10</v>
+      </c>
+      <c r="R8">
+        <v>9.2578621607288092</v>
+      </c>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>5176410</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A9,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Clarke Jackson</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A9,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A9,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>JR</v>
+      </c>
+      <c r="E9">
+        <v>17</v>
+      </c>
+      <c r="F9">
+        <v>8.7810656958654505</v>
+      </c>
+      <c r="G9">
+        <v>48</v>
+      </c>
+      <c r="H9">
+        <v>9.6907432085664809</v>
+      </c>
+      <c r="I9">
+        <v>102</v>
+      </c>
+      <c r="J9">
+        <v>9.3472886152019292</v>
+      </c>
+      <c r="K9">
+        <v>227</v>
+      </c>
+      <c r="L9">
+        <v>9.9946161188710505</v>
+      </c>
+      <c r="M9">
+        <v>98</v>
+      </c>
+      <c r="N9">
+        <v>10.3885003365457</v>
+      </c>
+      <c r="O9">
+        <v>45</v>
+      </c>
+      <c r="P9">
+        <v>10.5208701700662</v>
+      </c>
+      <c r="Q9">
+        <v>20</v>
+      </c>
+      <c r="R9">
+        <v>10.0832779833892</v>
+      </c>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>5241809</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A10,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Paige Engels</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A10,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A10,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SO</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>11.5046273983614</v>
+      </c>
+      <c r="G10">
+        <v>31</v>
+      </c>
+      <c r="H10">
+        <v>12.5200217590306</v>
+      </c>
+      <c r="I10">
+        <v>75</v>
+      </c>
+      <c r="J10">
+        <v>13.1851361694403</v>
+      </c>
+      <c r="K10">
+        <v>160</v>
+      </c>
+      <c r="L10">
+        <v>12.653435921926899</v>
+      </c>
+      <c r="M10">
+        <v>58</v>
+      </c>
+      <c r="N10">
+        <v>12.3931041531975</v>
+      </c>
+      <c r="O10">
+        <v>17</v>
+      </c>
+      <c r="P10">
+        <v>12.537646704230699</v>
+      </c>
+      <c r="Q10">
+        <v>5</v>
+      </c>
+      <c r="R10">
+        <v>8.5551277201844496</v>
+      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>5241811</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A11,rosters!$F:$F,rosters!$M:$M)</f>
+        <v>Audrey Chen</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A11,rosters!$F:$F,rosters!$H:$H)</f>
+        <v>G</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>_xlfn.XLOOKUP($A11,rosters!$F:$F,rosters!$N:$N)</f>
+        <v>SO</v>
+      </c>
+      <c r="E11">
+        <v>16</v>
+      </c>
+      <c r="F11">
+        <v>17.1303369338276</v>
+      </c>
+      <c r="G11">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>18.923484694660299</v>
+      </c>
+      <c r="I11">
+        <v>62</v>
+      </c>
+      <c r="J11">
+        <v>19.712737776994398</v>
+      </c>
+      <c r="K11">
+        <v>118</v>
+      </c>
+      <c r="L11">
+        <v>18.808792102193902</v>
+      </c>
+      <c r="M11">
+        <v>31</v>
+      </c>
+      <c r="N11">
+        <v>17.465338933348001</v>
+      </c>
+      <c r="O11">
+        <v>8</v>
+      </c>
+      <c r="P11">
+        <v>18.729008979345998</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>26.400757564888099</v>
+      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29D794C9-0982-465F-AD09-D98EC9197F09}">
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="str">
+        <f>parsedDistance!B2</f>
+        <v>Cooper Noard</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>parsedDistance!C2</f>
+        <v>G</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f>parsedDistance!D2</f>
+        <v>SR</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>ROUND(parsedDistance!F2,2)&amp;" ("&amp;parsedDistance!E2&amp;")"</f>
+        <v>16.87 (26)</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f>ROUND(parsedDistance!H2,2)&amp;" ("&amp;parsedDistance!G2&amp;")"</f>
+        <v>15.77 (67)</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f>ROUND(parsedDistance!J2,2)&amp;" ("&amp;parsedDistance!I2&amp;")"</f>
+        <v>17.42 (155)</v>
+      </c>
+      <c r="G2" s="1" t="str">
+        <f>ROUND(parsedDistance!L2,2)&amp;" ("&amp;parsedDistance!K2&amp;")"</f>
+        <v>17.78 (346)</v>
+      </c>
+      <c r="H2" s="1" t="str">
+        <f>ROUND(parsedDistance!N2,2)&amp;" ("&amp;parsedDistance!M2&amp;")"</f>
+        <v>18.26 (163)</v>
+      </c>
+      <c r="I2" s="1" t="str">
+        <f>ROUND(parsedDistance!P2,2)&amp;" ("&amp;parsedDistance!O2&amp;")"</f>
+        <v>16.84 (69)</v>
+      </c>
+      <c r="J2" s="1" t="str">
+        <f>ROUND(parsedDistance!R2,2)&amp;" ("&amp;parsedDistance!Q2&amp;")"</f>
+        <v>17.32 (30)</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="str">
+        <f>parsedDistance!B3</f>
+        <v>Jake Fiegen</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f>parsedDistance!C3</f>
+        <v>G</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f>parsedDistance!D3</f>
+        <v>SR</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f>ROUND(parsedDistance!F3,2)&amp;" ("&amp;parsedDistance!E3&amp;")"</f>
+        <v>11.96 (24)</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f>ROUND(parsedDistance!H3,2)&amp;" ("&amp;parsedDistance!G3&amp;")"</f>
+        <v>13.36 (50)</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <f>ROUND(parsedDistance!J3,2)&amp;" ("&amp;parsedDistance!I3&amp;")"</f>
+        <v>14.32 (111)</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <f>ROUND(parsedDistance!L3,2)&amp;" ("&amp;parsedDistance!K3&amp;")"</f>
+        <v>14.89 (269)</v>
+      </c>
+      <c r="H3" s="1" t="str">
+        <f>ROUND(parsedDistance!N3,2)&amp;" ("&amp;parsedDistance!M3&amp;")"</f>
+        <v>14.26 (134)</v>
+      </c>
+      <c r="I3" s="1" t="str">
+        <f>ROUND(parsedDistance!P3,2)&amp;" ("&amp;parsedDistance!O3&amp;")"</f>
+        <v>15.12 (70)</v>
+      </c>
+      <c r="J3" s="1" t="str">
+        <f>ROUND(parsedDistance!R3,2)&amp;" ("&amp;parsedDistance!Q3&amp;")"</f>
+        <v>16.5 (37)</v>
+      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="str">
+        <f>parsedDistance!B4</f>
+        <v>Adam Hinton</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <f>parsedDistance!C4</f>
+        <v>G</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <f>parsedDistance!D4</f>
+        <v>SR</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f>ROUND(parsedDistance!F4,2)&amp;" ("&amp;parsedDistance!E4&amp;")"</f>
+        <v>10.45 (18)</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f>ROUND(parsedDistance!H4,2)&amp;" ("&amp;parsedDistance!G4&amp;")"</f>
+        <v>14.4 (49)</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f>ROUND(parsedDistance!J4,2)&amp;" ("&amp;parsedDistance!I4&amp;")"</f>
+        <v>14.68 (119)</v>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f>ROUND(parsedDistance!L4,2)&amp;" ("&amp;parsedDistance!K4&amp;")"</f>
+        <v>16.27 (259)</v>
+      </c>
+      <c r="H4" s="1" t="str">
+        <f>ROUND(parsedDistance!N4,2)&amp;" ("&amp;parsedDistance!M4&amp;")"</f>
+        <v>17.78 (112)</v>
+      </c>
+      <c r="I4" s="1" t="str">
+        <f>ROUND(parsedDistance!P4,2)&amp;" ("&amp;parsedDistance!O4&amp;")"</f>
+        <v>17.67 (42)</v>
+      </c>
+      <c r="J4" s="1" t="str">
+        <f>ROUND(parsedDistance!R4,2)&amp;" ("&amp;parsedDistance!Q4&amp;")"</f>
+        <v>17.53 (15)</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="str">
+        <f>parsedDistance!B5</f>
+        <v>Jacob Beccles</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f>parsedDistance!C5</f>
+        <v>G</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f>parsedDistance!D5</f>
+        <v>JR</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>ROUND(parsedDistance!F5,2)&amp;" ("&amp;parsedDistance!E5&amp;")"</f>
+        <v>8.2 (11)</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>ROUND(parsedDistance!H5,2)&amp;" ("&amp;parsedDistance!G5&amp;")"</f>
+        <v>10.85 (28)</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <f>ROUND(parsedDistance!J5,2)&amp;" ("&amp;parsedDistance!I5&amp;")"</f>
+        <v>11.75 (70)</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f>ROUND(parsedDistance!L5,2)&amp;" ("&amp;parsedDistance!K5&amp;")"</f>
+        <v>11.38 (170)</v>
+      </c>
+      <c r="H5" s="1" t="str">
+        <f>ROUND(parsedDistance!N5,2)&amp;" ("&amp;parsedDistance!M5&amp;")"</f>
+        <v>11.62 (72)</v>
+      </c>
+      <c r="I5" s="1" t="str">
+        <f>ROUND(parsedDistance!P5,2)&amp;" ("&amp;parsedDistance!O5&amp;")"</f>
+        <v>12.14 (34)</v>
+      </c>
+      <c r="J5" s="1" t="str">
+        <f>ROUND(parsedDistance!R5,2)&amp;" ("&amp;parsedDistance!Q5&amp;")"</f>
+        <v>10.87 (15)</v>
+      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="str">
+        <f>parsedDistance!B6</f>
+        <v>Josh Baldwin</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <f>parsedDistance!C6</f>
+        <v>G</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f>parsedDistance!D6</f>
+        <v>SR</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>ROUND(parsedDistance!F6,2)&amp;" ("&amp;parsedDistance!E6&amp;")"</f>
+        <v>13.88 (10)</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>ROUND(parsedDistance!H6,2)&amp;" ("&amp;parsedDistance!G6&amp;")"</f>
+        <v>13.4 (26)</v>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f>ROUND(parsedDistance!J6,2)&amp;" ("&amp;parsedDistance!I6&amp;")"</f>
+        <v>11.46 (63)</v>
+      </c>
+      <c r="G6" s="1" t="str">
+        <f>ROUND(parsedDistance!L6,2)&amp;" ("&amp;parsedDistance!K6&amp;")"</f>
+        <v>13.12 (138)</v>
+      </c>
+      <c r="H6" s="1" t="str">
+        <f>ROUND(parsedDistance!N6,2)&amp;" ("&amp;parsedDistance!M6&amp;")"</f>
+        <v>14.6 (50)</v>
+      </c>
+      <c r="I6" s="1" t="str">
+        <f>ROUND(parsedDistance!P6,2)&amp;" ("&amp;parsedDistance!O6&amp;")"</f>
+        <v>17.38 (17)</v>
+      </c>
+      <c r="J6" s="1" t="str">
+        <f>ROUND(parsedDistance!R6,2)&amp;" ("&amp;parsedDistance!Q6&amp;")"</f>
+        <v>14.67 (6)</v>
+      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="str">
+        <f>parsedDistance!B7</f>
+        <v>Emily Pape</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f>parsedDistance!C7</f>
+        <v>F</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>parsedDistance!D7</f>
+        <v>SR</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>ROUND(parsedDistance!F7,2)&amp;" ("&amp;parsedDistance!E7&amp;")"</f>
+        <v>17.88 (36)</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>ROUND(parsedDistance!H7,2)&amp;" ("&amp;parsedDistance!G7&amp;")"</f>
+        <v>19.02 (79)</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f>ROUND(parsedDistance!J7,2)&amp;" ("&amp;parsedDistance!I7&amp;")"</f>
+        <v>18.76 (159)</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f>ROUND(parsedDistance!L7,2)&amp;" ("&amp;parsedDistance!K7&amp;")"</f>
+        <v>18.85 (283)</v>
+      </c>
+      <c r="H7" s="1" t="str">
+        <f>ROUND(parsedDistance!N7,2)&amp;" ("&amp;parsedDistance!M7&amp;")"</f>
+        <v>19.2 (97)</v>
+      </c>
+      <c r="I7" s="1" t="str">
+        <f>ROUND(parsedDistance!P7,2)&amp;" ("&amp;parsedDistance!O7&amp;")"</f>
+        <v>18.08 (28)</v>
+      </c>
+      <c r="J7" s="1" t="str">
+        <f>ROUND(parsedDistance!R7,2)&amp;" ("&amp;parsedDistance!Q7&amp;")"</f>
+        <v>16.74 (9)</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="str">
+        <f>parsedDistance!B8</f>
+        <v>Rachel Kaus</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f>parsedDistance!C8</f>
+        <v>G</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f>parsedDistance!D8</f>
+        <v>JR</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f>ROUND(parsedDistance!F8,2)&amp;" ("&amp;parsedDistance!E8&amp;")"</f>
+        <v>9.82 (31)</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f>ROUND(parsedDistance!H8,2)&amp;" ("&amp;parsedDistance!G8&amp;")"</f>
+        <v>9.32 (67)</v>
+      </c>
+      <c r="F8" s="1" t="str">
+        <f>ROUND(parsedDistance!J8,2)&amp;" ("&amp;parsedDistance!I8&amp;")"</f>
+        <v>8.48 (138)</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f>ROUND(parsedDistance!L8,2)&amp;" ("&amp;parsedDistance!K8&amp;")"</f>
+        <v>9.23 (275)</v>
+      </c>
+      <c r="H8" s="1" t="str">
+        <f>ROUND(parsedDistance!N8,2)&amp;" ("&amp;parsedDistance!M8&amp;")"</f>
+        <v>10.45 (110)</v>
+      </c>
+      <c r="I8" s="1" t="str">
+        <f>ROUND(parsedDistance!P8,2)&amp;" ("&amp;parsedDistance!O8&amp;")"</f>
+        <v>10.55 (41)</v>
+      </c>
+      <c r="J8" s="1" t="str">
+        <f>ROUND(parsedDistance!R8,2)&amp;" ("&amp;parsedDistance!Q8&amp;")"</f>
+        <v>9.26 (10)</v>
+      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="str">
+        <f>parsedDistance!B9</f>
+        <v>Clarke Jackson</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f>parsedDistance!C9</f>
+        <v>G</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f>parsedDistance!D9</f>
+        <v>JR</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f>ROUND(parsedDistance!F9,2)&amp;" ("&amp;parsedDistance!E9&amp;")"</f>
+        <v>8.78 (17)</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f>ROUND(parsedDistance!H9,2)&amp;" ("&amp;parsedDistance!G9&amp;")"</f>
+        <v>9.69 (48)</v>
+      </c>
+      <c r="F9" s="1" t="str">
+        <f>ROUND(parsedDistance!J9,2)&amp;" ("&amp;parsedDistance!I9&amp;")"</f>
+        <v>9.35 (102)</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f>ROUND(parsedDistance!L9,2)&amp;" ("&amp;parsedDistance!K9&amp;")"</f>
+        <v>9.99 (227)</v>
+      </c>
+      <c r="H9" s="1" t="str">
+        <f>ROUND(parsedDistance!N9,2)&amp;" ("&amp;parsedDistance!M9&amp;")"</f>
+        <v>10.39 (98)</v>
+      </c>
+      <c r="I9" s="1" t="str">
+        <f>ROUND(parsedDistance!P9,2)&amp;" ("&amp;parsedDistance!O9&amp;")"</f>
+        <v>10.52 (45)</v>
+      </c>
+      <c r="J9" s="1" t="str">
+        <f>ROUND(parsedDistance!R9,2)&amp;" ("&amp;parsedDistance!Q9&amp;")"</f>
+        <v>10.08 (20)</v>
+      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="str">
+        <f>parsedDistance!B10</f>
+        <v>Paige Engels</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>parsedDistance!C10</f>
+        <v>G</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f>parsedDistance!D10</f>
+        <v>SO</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>ROUND(parsedDistance!F10,2)&amp;" ("&amp;parsedDistance!E10&amp;")"</f>
+        <v>11.5 (10)</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f>ROUND(parsedDistance!H10,2)&amp;" ("&amp;parsedDistance!G10&amp;")"</f>
+        <v>12.52 (31)</v>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f>ROUND(parsedDistance!J10,2)&amp;" ("&amp;parsedDistance!I10&amp;")"</f>
+        <v>13.19 (75)</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f>ROUND(parsedDistance!L10,2)&amp;" ("&amp;parsedDistance!K10&amp;")"</f>
+        <v>12.65 (160)</v>
+      </c>
+      <c r="H10" s="1" t="str">
+        <f>ROUND(parsedDistance!N10,2)&amp;" ("&amp;parsedDistance!M10&amp;")"</f>
+        <v>12.39 (58)</v>
+      </c>
+      <c r="I10" s="1" t="str">
+        <f>ROUND(parsedDistance!P10,2)&amp;" ("&amp;parsedDistance!O10&amp;")"</f>
+        <v>12.54 (17)</v>
+      </c>
+      <c r="J10" s="1" t="str">
+        <f>ROUND(parsedDistance!R10,2)&amp;" ("&amp;parsedDistance!Q10&amp;")"</f>
+        <v>8.56 (5)</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="str">
+        <f>parsedDistance!B11</f>
+        <v>Audrey Chen</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>parsedDistance!C11</f>
+        <v>G</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f>parsedDistance!D11</f>
+        <v>SO</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>ROUND(parsedDistance!F11,2)&amp;" ("&amp;parsedDistance!E11&amp;")"</f>
+        <v>17.13 (16)</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f>ROUND(parsedDistance!H11,2)&amp;" ("&amp;parsedDistance!G11&amp;")"</f>
+        <v>18.92 (30)</v>
+      </c>
+      <c r="F11" s="1" t="str">
+        <f>ROUND(parsedDistance!J11,2)&amp;" ("&amp;parsedDistance!I11&amp;")"</f>
+        <v>19.71 (62)</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f>ROUND(parsedDistance!L11,2)&amp;" ("&amp;parsedDistance!K11&amp;")"</f>
+        <v>18.81 (118)</v>
+      </c>
+      <c r="H11" s="1" t="str">
+        <f>ROUND(parsedDistance!N11,2)&amp;" ("&amp;parsedDistance!M11&amp;")"</f>
+        <v>17.47 (31)</v>
+      </c>
+      <c r="I11" s="1" t="str">
+        <f>ROUND(parsedDistance!P11,2)&amp;" ("&amp;parsedDistance!O11&amp;")"</f>
+        <v>18.73 (8)</v>
+      </c>
+      <c r="J11" s="1" t="str">
+        <f>ROUND(parsedDistance!R11,2)&amp;" ("&amp;parsedDistance!Q11&amp;")"</f>
+        <v>26.4 (1)</v>
+      </c>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>304</v>
+      </c>
+      <c r="D13" s="5">
+        <f>SUMPRODUCT(parsedDistance!F2:F11,parsedDistance!E2:E11)/SUM(parsedDistance!E2:E11)</f>
+        <v>13.211506797376039</v>
+      </c>
+      <c r="E13" s="5">
+        <f>SUMPRODUCT(parsedDistance!H2:H11,parsedDistance!G2:G11)/SUM(parsedDistance!G2:G11)</f>
+        <v>13.958310608204092</v>
+      </c>
+      <c r="F13" s="5">
+        <f>SUMPRODUCT(parsedDistance!J2:J11,parsedDistance!I2:I11)/SUM(parsedDistance!I2:I11)</f>
+        <v>14.135151551332827</v>
+      </c>
+      <c r="G13" s="5">
+        <f>SUMPRODUCT(parsedDistance!L2:L11,parsedDistance!K2:K11)/SUM(parsedDistance!K2:K11)</f>
+        <v>14.478780767121773</v>
+      </c>
+      <c r="H13" s="5">
+        <f>SUMPRODUCT(parsedDistance!N2:N11,parsedDistance!M2:M11)/SUM(parsedDistance!M2:M11)</f>
+        <v>14.848435560714588</v>
+      </c>
+      <c r="I13" s="5">
+        <f>SUMPRODUCT(parsedDistance!P2:P11,parsedDistance!O2:O11)/SUM(parsedDistance!O2:O11)</f>
+        <v>14.680093627093433</v>
+      </c>
+      <c r="J13" s="5">
+        <f>SUMPRODUCT(parsedDistance!R2:R11,parsedDistance!Q2:Q11)/SUM(parsedDistance!Q2:Q11)</f>
+        <v>14.580090413291115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBAA3874-6021-4AD9-BC15-4CB250AE0C24}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
